--- a/src/main/resources/datasets/Import_Chartres.xlsx
+++ b/src/main/resources/datasets/Import_Chartres.xlsx
@@ -66,7 +66,7 @@
         <color indexed="11"/>
         <rFont val="Arial"/>
       </rPr>
-      <t>https://thesaurus.mom.fr/?idt=th230</t>
+      <t>https://thesaurus.mom.fr/?idt=th258</t>
     </r>
   </si>
   <si>
@@ -938,7 +938,7 @@
         <color indexed="11"/>
         <rFont val="Arial"/>
       </rPr>
-      <t>https://thesaurus.mom.fr/?idc=4288312&amp;idt=th230</t>
+      <t>https://thesaurus.mom.fr/?idc=4289298&amp;idt=th258</t>
     </r>
   </si>
   <si>
@@ -988,7 +988,7 @@
         <color indexed="11"/>
         <rFont val="Arial"/>
       </rPr>
-      <t>https://thesaurus.mom.fr/?idc=4288313&amp;idt=th230</t>
+      <t>https://thesaurus.mom.fr/?idc=4289299&amp;idt=th258</t>
     </r>
   </si>
   <si>
@@ -3352,10 +3352,10 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="12.6667" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="37.7891" style="1" customWidth="1"/>
+    <col min="1" max="1" width="37.8516" style="1" customWidth="1"/>
     <col min="2" max="2" width="54" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="46.1953" style="1" customWidth="1"/>
+    <col min="4" max="4" width="46.1719" style="1" customWidth="1"/>
     <col min="5" max="5" width="30" style="1" customWidth="1"/>
     <col min="6" max="16384" width="12.6719" style="1" customWidth="1"/>
   </cols>
@@ -3463,7 +3463,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" location="" tooltip="" display="admin@siamois.fr"/>
-    <hyperlink ref="E2" r:id="rId2" location="" tooltip="" display="https://thesaurus.mom.fr/?idt=th230"/>
+    <hyperlink ref="E2" r:id="rId2" location="" tooltip="" display="https://thesaurus.mom.fr/?idt=th258"/>
     <hyperlink ref="E3" r:id="rId3" location="" tooltip="" display="https://thesaurus.mom.fr/?idt=th240"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
@@ -30487,7 +30487,7 @@
     <col min="2" max="2" width="37.8516" style="40" customWidth="1"/>
     <col min="3" max="3" width="21.3516" style="40" customWidth="1"/>
     <col min="4" max="4" width="12.6719" style="40" customWidth="1"/>
-    <col min="5" max="5" width="115.367" style="40" customWidth="1"/>
+    <col min="5" max="5" width="115.352" style="40" customWidth="1"/>
     <col min="6" max="16384" width="12.6719" style="40" customWidth="1"/>
   </cols>
   <sheetData>
@@ -47323,26 +47323,26 @@
     <hyperlink ref="C58" r:id="rId151" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th230"/>
     <hyperlink ref="C59" r:id="rId152" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th230"/>
     <hyperlink ref="C60" r:id="rId153" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th230"/>
-    <hyperlink ref="C61" r:id="rId154" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4288312&amp;idt=th230"/>
-    <hyperlink ref="C62" r:id="rId155" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4288312&amp;idt=th230"/>
-    <hyperlink ref="C63" r:id="rId156" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4288312&amp;idt=th230"/>
-    <hyperlink ref="C64" r:id="rId157" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4288312&amp;idt=th230"/>
-    <hyperlink ref="C65" r:id="rId158" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4288312&amp;idt=th230"/>
-    <hyperlink ref="C66" r:id="rId159" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4288312&amp;idt=th230"/>
-    <hyperlink ref="C67" r:id="rId160" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4288312&amp;idt=th230"/>
-    <hyperlink ref="C68" r:id="rId161" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4288312&amp;idt=th230"/>
-    <hyperlink ref="C69" r:id="rId162" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4288312&amp;idt=th230"/>
-    <hyperlink ref="C70" r:id="rId163" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4288312&amp;idt=th230"/>
-    <hyperlink ref="C71" r:id="rId164" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4288312&amp;idt=th230"/>
-    <hyperlink ref="C72" r:id="rId165" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4288312&amp;idt=th230"/>
-    <hyperlink ref="C73" r:id="rId166" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4288312&amp;idt=th230"/>
-    <hyperlink ref="C74" r:id="rId167" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4288313&amp;idt=th230"/>
-    <hyperlink ref="C75" r:id="rId168" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4288313&amp;idt=th230"/>
-    <hyperlink ref="C76" r:id="rId169" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4288313&amp;idt=th230"/>
-    <hyperlink ref="C77" r:id="rId170" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4288313&amp;idt=th230"/>
-    <hyperlink ref="C78" r:id="rId171" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4288313&amp;idt=th230"/>
-    <hyperlink ref="C79" r:id="rId172" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4288313&amp;idt=th230"/>
-    <hyperlink ref="C80" r:id="rId173" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4288313&amp;idt=th230"/>
+    <hyperlink ref="C61" r:id="rId154" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4289298&amp;idt=th258"/>
+    <hyperlink ref="C62" r:id="rId155" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4289298&amp;idt=th258"/>
+    <hyperlink ref="C63" r:id="rId156" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4289298&amp;idt=th258"/>
+    <hyperlink ref="C64" r:id="rId157" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4289298&amp;idt=th258"/>
+    <hyperlink ref="C65" r:id="rId158" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4289298&amp;idt=th258"/>
+    <hyperlink ref="C66" r:id="rId159" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4289298&amp;idt=th258"/>
+    <hyperlink ref="C67" r:id="rId160" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4289298&amp;idt=th258"/>
+    <hyperlink ref="C68" r:id="rId161" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4289298&amp;idt=th258"/>
+    <hyperlink ref="C69" r:id="rId162" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4289298&amp;idt=th258"/>
+    <hyperlink ref="C70" r:id="rId163" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4289298&amp;idt=th258"/>
+    <hyperlink ref="C71" r:id="rId164" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4289298&amp;idt=th258"/>
+    <hyperlink ref="C72" r:id="rId165" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4289298&amp;idt=th258"/>
+    <hyperlink ref="C73" r:id="rId166" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4289298&amp;idt=th258"/>
+    <hyperlink ref="C74" r:id="rId167" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4289299&amp;idt=th258"/>
+    <hyperlink ref="C75" r:id="rId168" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4289299&amp;idt=th258"/>
+    <hyperlink ref="C76" r:id="rId169" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4289299&amp;idt=th258"/>
+    <hyperlink ref="C77" r:id="rId170" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4289299&amp;idt=th258"/>
+    <hyperlink ref="C78" r:id="rId171" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4289299&amp;idt=th258"/>
+    <hyperlink ref="C79" r:id="rId172" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4289299&amp;idt=th258"/>
+    <hyperlink ref="C80" r:id="rId173" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4289299&amp;idt=th258"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>

--- a/src/main/resources/datasets/Import_Chartres.xlsx
+++ b/src/main/resources/datasets/Import_Chartres.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="363">
   <si>
     <t>Nom</t>
   </si>
@@ -73,7 +73,7 @@
     <t>Test 1</t>
   </si>
   <si>
-    <t>Astuce pour importer le thesaurus 240 dans le système sans effort</t>
+    <t xml:space="preserve">Astuce pour importer le thesaurus 240 dans le système </t>
   </si>
   <si>
     <t>hack1</t>
@@ -90,6 +90,26 @@
         <rFont val="Arial"/>
       </rPr>
       <t>https://thesaurus.mom.fr/?idt=th240</t>
+    </r>
+  </si>
+  <si>
+    <t>Test th230</t>
+  </si>
+  <si>
+    <t>Astuce pour importer le thesaurus 230 dans le systèm</t>
+  </si>
+  <si>
+    <t>hack2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="11"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>https://thesaurus.mom.fr/?idt=th230</t>
     </r>
   </si>
   <si>
@@ -3412,11 +3432,21 @@
       </c>
     </row>
     <row r="4" ht="13.65" customHeight="1">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
+      <c r="A4" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s" s="3">
+        <v>18</v>
+      </c>
     </row>
     <row r="5" ht="13.65" customHeight="1">
       <c r="A5" s="4"/>
@@ -3465,6 +3495,7 @@
     <hyperlink ref="D2" r:id="rId1" location="" tooltip="" display="admin@siamois.fr"/>
     <hyperlink ref="E2" r:id="rId2" location="" tooltip="" display="https://thesaurus.mom.fr/?idt=th258"/>
     <hyperlink ref="E3" r:id="rId3" location="" tooltip="" display="https://thesaurus.mom.fr/?idt=th240"/>
+    <hyperlink ref="E4" r:id="rId4" location="" tooltip="" display="https://thesaurus.mom.fr/?idt=th230"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
@@ -3491,23 +3522,23 @@
   <sheetData>
     <row r="1" ht="13.65" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B1" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C1" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
     </row>
     <row r="2" ht="13.65" customHeight="1">
       <c r="A2" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -3515,10 +3546,10 @@
     </row>
     <row r="3" ht="13.65" customHeight="1">
       <c r="A3" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -3526,10 +3557,10 @@
     </row>
     <row r="4" ht="13.65" customHeight="1">
       <c r="A4" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -3537,10 +3568,10 @@
     </row>
     <row r="5" ht="13.65" customHeight="1">
       <c r="A5" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -3548,10 +3579,10 @@
     </row>
     <row r="6" ht="13.65" customHeight="1">
       <c r="A6" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -3559,10 +3590,10 @@
     </row>
     <row r="7" ht="13.65" customHeight="1">
       <c r="A7" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -3570,10 +3601,10 @@
     </row>
     <row r="8" ht="13.65" customHeight="1">
       <c r="A8" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -3619,26 +3650,26 @@
   <sheetData>
     <row r="1" ht="13.65" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B1" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C1" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D1" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E1" s="4"/>
     </row>
     <row r="2" ht="13.65" customHeight="1">
       <c r="A2" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D2" t="s" s="2">
         <v>0</v>
@@ -3647,11 +3678,11 @@
     </row>
     <row r="3" ht="13.65" customHeight="1">
       <c r="A3" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="D3" t="s" s="2">
         <v>1</v>
@@ -3660,11 +3691,11 @@
     </row>
     <row r="4" ht="13.65" customHeight="1">
       <c r="A4" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D4" t="s" s="2">
         <v>2</v>
@@ -3673,11 +3704,11 @@
     </row>
     <row r="5" ht="13.65" customHeight="1">
       <c r="A5" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>3</v>
@@ -3686,11 +3717,11 @@
     </row>
     <row r="6" ht="13.65" customHeight="1">
       <c r="A6" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D6" t="s" s="2">
         <v>4</v>
@@ -3699,24 +3730,24 @@
     </row>
     <row r="7" ht="13.65" customHeight="1">
       <c r="A7" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E7" s="4"/>
     </row>
     <row r="8" ht="13.65" customHeight="1">
       <c r="A8" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="D8" t="s" s="2">
         <v>0</v>
@@ -3725,24 +3756,24 @@
     </row>
     <row r="9" ht="13.65" customHeight="1">
       <c r="A9" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E9" s="4"/>
     </row>
     <row r="10" ht="13.65" customHeight="1">
       <c r="A10" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>2</v>
@@ -3751,11 +3782,11 @@
     </row>
     <row r="11" ht="13.65" customHeight="1">
       <c r="A11" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>0</v>
@@ -3764,89 +3795,89 @@
     </row>
     <row r="12" ht="13.65" customHeight="1">
       <c r="A12" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E12" s="4"/>
     </row>
     <row r="13" ht="13.65" customHeight="1">
       <c r="A13" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E13" s="4"/>
     </row>
     <row r="14" ht="13.65" customHeight="1">
       <c r="A14" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E14" s="4"/>
     </row>
     <row r="15" ht="13.65" customHeight="1">
       <c r="A15" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E15" s="4"/>
     </row>
     <row r="16" ht="13.65" customHeight="1">
       <c r="A16" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E16" s="4"/>
     </row>
     <row r="17" ht="13.65" customHeight="1">
       <c r="A17" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E17" s="4"/>
     </row>
     <row r="18" ht="13.65" customHeight="1">
       <c r="A18" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>0</v>
@@ -3855,11 +3886,11 @@
     </row>
     <row r="19" ht="13.65" customHeight="1">
       <c r="A19" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>2</v>
@@ -3868,92 +3899,92 @@
     </row>
     <row r="20" ht="13.65" customHeight="1">
       <c r="A20" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E20" s="4"/>
     </row>
     <row r="21" ht="13.65" customHeight="1">
       <c r="A21" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E21" s="4"/>
     </row>
     <row r="22" ht="13.65" customHeight="1">
       <c r="A22" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E22" s="4"/>
     </row>
     <row r="23" ht="13.65" customHeight="1">
       <c r="A23" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E23" s="4"/>
     </row>
     <row r="24" ht="13.65" customHeight="1">
       <c r="A24" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E24" s="4"/>
     </row>
     <row r="25" ht="13.65" customHeight="1">
       <c r="A25" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E25" s="4"/>
     </row>
     <row r="26" ht="13.65" customHeight="1">
       <c r="A26" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E26" s="4"/>
     </row>
@@ -3980,10 +4011,10 @@
   <sheetData>
     <row r="1" ht="13.65" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B1" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -3991,10 +4022,10 @@
     </row>
     <row r="2" ht="13.65" customHeight="1">
       <c r="A2" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -11010,13 +11041,13 @@
   <sheetData>
     <row r="1" ht="13.65" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B1" t="s" s="2">
         <v>0</v>
       </c>
       <c r="C1" t="s" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D1" t="s" s="2">
         <v>2</v>
@@ -11025,46 +11056,46 @@
     </row>
     <row r="2" ht="13.65" customHeight="1">
       <c r="A2" t="s" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E2" s="4"/>
     </row>
     <row r="3" ht="13.65" customHeight="1">
       <c r="A3" t="s" s="6">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E3" s="4"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="s" s="7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s" s="8">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E4" s="4"/>
     </row>
@@ -11073,13 +11104,13 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E5" s="4"/>
     </row>
@@ -11146,10 +11177,10 @@
   <sheetData>
     <row r="1" ht="13.65" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s" s="2">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -11157,10 +11188,10 @@
     </row>
     <row r="2" ht="13.65" customHeight="1">
       <c r="A2" t="s" s="2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s" s="3">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -11168,10 +11199,10 @@
     </row>
     <row r="3" ht="13.65" customHeight="1">
       <c r="A3" t="s" s="2">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s" s="3">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -11179,10 +11210,10 @@
     </row>
     <row r="4" ht="13.65" customHeight="1">
       <c r="A4" t="s" s="2">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s" s="3">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -11190,10 +11221,10 @@
     </row>
     <row r="5" ht="13.65" customHeight="1">
       <c r="A5" t="s" s="2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -11201,10 +11232,10 @@
     </row>
     <row r="6" ht="13.65" customHeight="1">
       <c r="A6" t="s" s="2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -11212,10 +11243,10 @@
     </row>
     <row r="7" ht="13.65" customHeight="1">
       <c r="A7" t="s" s="2">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -11223,10 +11254,10 @@
     </row>
     <row r="8" ht="13.65" customHeight="1">
       <c r="A8" t="s" s="2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -11234,10 +11265,10 @@
     </row>
     <row r="9" ht="13.65" customHeight="1">
       <c r="A9" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>43</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>39</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -11245,10 +11276,10 @@
     </row>
     <row r="10" ht="13.65" customHeight="1">
       <c r="A10" t="s" s="2">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -11256,10 +11287,10 @@
     </row>
     <row r="11" ht="13.65" customHeight="1">
       <c r="A11" t="s" s="11">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -11267,10 +11298,10 @@
     </row>
     <row r="12" ht="15.35" customHeight="1">
       <c r="A12" t="s" s="12">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s" s="13">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -18210,42 +18241,42 @@
         <v>2</v>
       </c>
       <c r="C1" t="s" s="16">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D1" t="s" s="16">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E1" t="s" s="16">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F1" t="s" s="16">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G1" t="s" s="16">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H1" t="s" s="16">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I1" t="s" s="2">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J1" t="s" s="2">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" ht="15.35" customHeight="1">
       <c r="A2" t="s" s="17">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s" s="17">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s" s="17">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s" s="18">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s" s="19">
         <v>13</v>
@@ -18260,24 +18291,24 @@
         <v>41107</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" ht="15.35" customHeight="1">
       <c r="A3" t="s" s="12">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B3" t="s" s="12">
+        <v>63</v>
+      </c>
+      <c r="C3" t="s" s="12">
+        <v>44</v>
+      </c>
+      <c r="D3" t="s" s="23">
         <v>59</v>
-      </c>
-      <c r="C3" t="s" s="12">
-        <v>40</v>
-      </c>
-      <c r="D3" t="s" s="23">
-        <v>55</v>
       </c>
       <c r="E3" t="s" s="19">
         <v>13</v>
@@ -18293,21 +18324,21 @@
       </c>
       <c r="I3" s="25"/>
       <c r="J3" t="s" s="2">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" ht="15.35" customHeight="1">
       <c r="A4" t="s" s="12">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B4" t="s" s="12">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s" s="12">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s" s="23">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s" s="19">
         <v>13</v>
@@ -18323,21 +18354,21 @@
       </c>
       <c r="I4" s="26"/>
       <c r="J4" t="s" s="27">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" ht="15.35" customHeight="1">
       <c r="A5" t="s" s="12">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s" s="12">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s" s="12">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s" s="23">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s" s="19">
         <v>13</v>
@@ -18353,21 +18384,21 @@
       </c>
       <c r="I5" s="26"/>
       <c r="J5" t="s" s="28">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" ht="15.35" customHeight="1">
       <c r="A6" t="s" s="12">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B6" t="s" s="12">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s" s="12">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s" s="23">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E6" t="s" s="19">
         <v>13</v>
@@ -18383,21 +18414,21 @@
       </c>
       <c r="I6" s="26"/>
       <c r="J6" t="s" s="28">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" ht="15.35" customHeight="1">
       <c r="A7" t="s" s="12">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B7" t="s" s="12">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s" s="12">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s" s="23">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s" s="19">
         <v>13</v>
@@ -18413,21 +18444,21 @@
       </c>
       <c r="I7" s="26"/>
       <c r="J7" t="s" s="28">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" ht="15.35" customHeight="1">
       <c r="A8" t="s" s="12">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s" s="12">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s" s="12">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s" s="23">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s" s="19">
         <v>13</v>
@@ -18443,21 +18474,21 @@
       </c>
       <c r="I8" s="26"/>
       <c r="J8" t="s" s="28">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" ht="15.35" customHeight="1">
       <c r="A9" t="s" s="12">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s" s="12">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s" s="12">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s" s="23">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s" s="19">
         <v>13</v>
@@ -18473,21 +18504,21 @@
       </c>
       <c r="I9" s="26"/>
       <c r="J9" t="s" s="28">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" ht="15.35" customHeight="1">
       <c r="A10" t="s" s="12">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s" s="12">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s" s="12">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s" s="23">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E10" t="s" s="19">
         <v>13</v>
@@ -18499,21 +18530,21 @@
       <c r="H10" s="26"/>
       <c r="I10" s="26"/>
       <c r="J10" t="s" s="28">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" ht="15.35" customHeight="1">
       <c r="A11" t="s" s="12">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B11" t="s" s="12">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s" s="12">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s" s="23">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E11" t="s" s="19">
         <v>13</v>
@@ -18529,21 +18560,21 @@
       </c>
       <c r="I11" s="26"/>
       <c r="J11" t="s" s="28">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" ht="15.35" customHeight="1">
       <c r="A12" t="s" s="12">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B12" t="s" s="12">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s" s="12">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s" s="23">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s" s="19">
         <v>13</v>
@@ -18555,19 +18586,19 @@
       <c r="H12" s="26"/>
       <c r="I12" s="26"/>
       <c r="J12" t="s" s="28">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" ht="15.35" customHeight="1">
       <c r="A13" t="s" s="12">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B13" t="s" s="12">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C13" s="28"/>
       <c r="D13" t="s" s="23">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s" s="19">
         <v>13</v>
@@ -18579,21 +18610,21 @@
       <c r="H13" s="26"/>
       <c r="I13" s="26"/>
       <c r="J13" t="s" s="28">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" ht="15.35" customHeight="1">
       <c r="A14" t="s" s="12">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s" s="12">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s" s="12">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s" s="23">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E14" t="s" s="19">
         <v>13</v>
@@ -18609,21 +18640,21 @@
       </c>
       <c r="I14" s="26"/>
       <c r="J14" t="s" s="28">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" ht="15.35" customHeight="1">
       <c r="A15" t="s" s="12">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s" s="12">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s" s="12">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s" s="23">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E15" t="s" s="17">
         <v>13</v>
@@ -18639,7 +18670,7 @@
       </c>
       <c r="I15" s="26"/>
       <c r="J15" t="s" s="28">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" ht="13.65" customHeight="1">
@@ -30496,24 +30527,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="2">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C1" t="s" s="16">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D1" t="s" s="2">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E1" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" ht="15.35" customHeight="1">
       <c r="A2" t="s" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B2" t="s" s="41">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s" s="19">
         <v>13</v>
@@ -30525,10 +30556,10 @@
     </row>
     <row r="3" ht="15.35" customHeight="1">
       <c r="A3" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B3" t="s" s="41">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s" s="19">
         <v>13</v>
@@ -30540,10 +30571,10 @@
     </row>
     <row r="4" ht="15.35" customHeight="1">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s" s="41">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s" s="19">
         <v>13</v>
@@ -30555,10 +30586,10 @@
     </row>
     <row r="5" ht="15.35" customHeight="1">
       <c r="A5" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s" s="41">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s" s="19">
         <v>13</v>
@@ -30570,10 +30601,10 @@
     </row>
     <row r="6" ht="15.35" customHeight="1">
       <c r="A6" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="B6" t="s" s="41">
         <v>93</v>
-      </c>
-      <c r="B6" t="s" s="41">
-        <v>89</v>
       </c>
       <c r="C6" t="s" s="19">
         <v>13</v>
@@ -30585,10 +30616,10 @@
     </row>
     <row r="7" ht="15.35" customHeight="1">
       <c r="A7" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B7" t="s" s="41">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s" s="19">
         <v>13</v>
@@ -30600,10 +30631,10 @@
     </row>
     <row r="8" ht="15.35" customHeight="1">
       <c r="A8" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B8" t="s" s="41">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s" s="19">
         <v>13</v>
@@ -30615,10 +30646,10 @@
     </row>
     <row r="9" ht="15.35" customHeight="1">
       <c r="A9" t="s" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B9" t="s" s="41">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s" s="19">
         <v>13</v>
@@ -30630,10 +30661,10 @@
     </row>
     <row r="10" ht="15.35" customHeight="1">
       <c r="A10" t="s" s="2">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B10" t="s" s="41">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s" s="19">
         <v>13</v>
@@ -30645,10 +30676,10 @@
     </row>
     <row r="11" ht="15.35" customHeight="1">
       <c r="A11" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B11" t="s" s="41">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s" s="19">
         <v>13</v>
@@ -30660,10 +30691,10 @@
     </row>
     <row r="12" ht="15.35" customHeight="1">
       <c r="A12" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B12" t="s" s="41">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s" s="19">
         <v>13</v>
@@ -30675,10 +30706,10 @@
     </row>
     <row r="13" ht="15.35" customHeight="1">
       <c r="A13" t="s" s="2">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B13" t="s" s="41">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s" s="19">
         <v>13</v>
@@ -30690,10 +30721,10 @@
     </row>
     <row r="14" ht="15.35" customHeight="1">
       <c r="A14" t="s" s="2">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B14" t="s" s="41">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s" s="19">
         <v>13</v>
@@ -30705,10 +30736,10 @@
     </row>
     <row r="15" ht="15.35" customHeight="1">
       <c r="A15" t="s" s="2">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B15" t="s" s="41">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s" s="19">
         <v>13</v>
@@ -30720,10 +30751,10 @@
     </row>
     <row r="16" ht="15.35" customHeight="1">
       <c r="A16" t="s" s="2">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B16" t="s" s="41">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s" s="19">
         <v>13</v>
@@ -30735,10 +30766,10 @@
     </row>
     <row r="17" ht="15.35" customHeight="1">
       <c r="A17" t="s" s="2">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B17" t="s" s="41">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s" s="19">
         <v>13</v>
@@ -30750,10 +30781,10 @@
     </row>
     <row r="18" ht="15.35" customHeight="1">
       <c r="A18" t="s" s="2">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B18" t="s" s="41">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s" s="19">
         <v>13</v>
@@ -30765,10 +30796,10 @@
     </row>
     <row r="19" ht="15.35" customHeight="1">
       <c r="A19" t="s" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B19" t="s" s="41">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s" s="19">
         <v>13</v>
@@ -30780,10 +30811,10 @@
     </row>
     <row r="20" ht="15.35" customHeight="1">
       <c r="A20" t="s" s="2">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B20" t="s" s="41">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C20" t="s" s="17">
         <v>13</v>
@@ -30792,7 +30823,7 @@
         <v>7</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -30856,64 +30887,64 @@
         <v>1</v>
       </c>
       <c r="C1" t="s" s="2">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D1" t="s" s="2">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E1" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F1" t="s" s="11">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G1" t="s" s="2">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H1" t="s" s="2">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I1" t="s" s="2">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J1" t="s" s="2">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="K1" t="s" s="2">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="L1" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="M1" t="s" s="2">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" ht="13.75" customHeight="1">
       <c r="A2" t="s" s="2">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C2" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D2" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E2" s="43"/>
       <c r="F2" t="s" s="44">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G2" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J2" s="45">
         <v>41081</v>
@@ -30921,34 +30952,34 @@
       <c r="K2" s="4"/>
       <c r="L2" s="2"/>
       <c r="M2" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" ht="13.75" customHeight="1">
       <c r="A3" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="C3" t="s" s="3">
         <v>124</v>
       </c>
-      <c r="B3" t="s" s="2">
+      <c r="D3" t="s" s="3">
         <v>125</v>
-      </c>
-      <c r="C3" t="s" s="3">
-        <v>120</v>
-      </c>
-      <c r="D3" t="s" s="3">
-        <v>121</v>
       </c>
       <c r="E3" s="43"/>
       <c r="F3" t="s" s="44">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G3" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J3" s="45">
         <v>41082</v>
@@ -30956,34 +30987,34 @@
       <c r="K3" s="4"/>
       <c r="L3" s="2"/>
       <c r="M3" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" ht="13.75" customHeight="1">
       <c r="A4" t="s" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C4" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D4" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E4" s="43"/>
       <c r="F4" t="s" s="44">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G4" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J4" s="45">
         <v>41082</v>
@@ -30991,34 +31022,34 @@
       <c r="K4" s="4"/>
       <c r="L4" s="2"/>
       <c r="M4" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" ht="13.75" customHeight="1">
       <c r="A5" t="s" s="2">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C5" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D5" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E5" s="43"/>
       <c r="F5" t="s" s="44">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G5" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J5" s="45">
         <v>41082</v>
@@ -31026,34 +31057,34 @@
       <c r="K5" s="4"/>
       <c r="L5" s="2"/>
       <c r="M5" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" ht="13.75" customHeight="1">
       <c r="A6" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C6" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D6" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E6" s="43"/>
       <c r="F6" t="s" s="44">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G6" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J6" s="45">
         <v>41091</v>
@@ -31061,34 +31092,34 @@
       <c r="K6" s="4"/>
       <c r="L6" s="2"/>
       <c r="M6" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" ht="13.75" customHeight="1">
       <c r="A7" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C7" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D7" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E7" s="43"/>
       <c r="F7" t="s" s="44">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G7" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J7" s="45">
         <v>41091</v>
@@ -31096,34 +31127,34 @@
       <c r="K7" s="4"/>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" ht="13.75" customHeight="1">
       <c r="A8" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C8" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D8" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E8" s="43"/>
       <c r="F8" t="s" s="44">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G8" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J8" s="45">
         <v>41091</v>
@@ -31131,34 +31162,34 @@
       <c r="K8" s="4"/>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" ht="13.75" customHeight="1">
       <c r="A9" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C9" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D9" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E9" s="43"/>
       <c r="F9" t="s" s="44">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G9" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J9" s="45">
         <v>41091</v>
@@ -31166,34 +31197,34 @@
       <c r="K9" s="4"/>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" ht="13.75" customHeight="1">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C10" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D10" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E10" s="43"/>
       <c r="F10" t="s" s="44">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G10" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J10" s="45">
         <v>41091</v>
@@ -31201,34 +31232,34 @@
       <c r="K10" s="4"/>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" ht="13.75" customHeight="1">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C11" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D11" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E11" s="43"/>
       <c r="F11" t="s" s="44">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G11" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J11" s="45">
         <v>41091</v>
@@ -31236,34 +31267,34 @@
       <c r="K11" s="4"/>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" ht="13.75" customHeight="1">
       <c r="A12" t="s" s="2">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C12" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D12" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E12" s="43"/>
       <c r="F12" t="s" s="44">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G12" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J12" s="45">
         <v>41091</v>
@@ -31271,34 +31302,34 @@
       <c r="K12" s="4"/>
       <c r="L12" s="2"/>
       <c r="M12" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" ht="13.75" customHeight="1">
       <c r="A13" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C13" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D13" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E13" s="43"/>
       <c r="F13" t="s" s="44">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G13" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J13" s="45">
         <v>41091</v>
@@ -31306,34 +31337,34 @@
       <c r="K13" s="4"/>
       <c r="L13" s="2"/>
       <c r="M13" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" ht="13.75" customHeight="1">
       <c r="A14" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C14" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D14" t="s" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E14" s="43"/>
       <c r="F14" t="s" s="44">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G14" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J14" s="45">
         <v>41091</v>
@@ -31341,34 +31372,34 @@
       <c r="K14" s="4"/>
       <c r="L14" s="2"/>
       <c r="M14" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" ht="13.75" customHeight="1">
       <c r="A15" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C15" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D15" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E15" s="43"/>
       <c r="F15" t="s" s="44">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G15" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J15" s="45">
         <v>41091</v>
@@ -31376,34 +31407,34 @@
       <c r="K15" s="4"/>
       <c r="L15" s="2"/>
       <c r="M15" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" ht="13.75" customHeight="1">
       <c r="A16" t="s" s="2">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C16" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D16" t="s" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E16" s="43"/>
       <c r="F16" t="s" s="44">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G16" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J16" s="45">
         <v>41091</v>
@@ -31411,34 +31442,34 @@
       <c r="K16" s="4"/>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" ht="13.75" customHeight="1">
       <c r="A17" t="s" s="2">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C17" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D17" t="s" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E17" s="43"/>
       <c r="F17" t="s" s="44">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G17" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J17" s="45">
         <v>41095</v>
@@ -31446,34 +31477,34 @@
       <c r="K17" s="4"/>
       <c r="L17" s="2"/>
       <c r="M17" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" ht="13.75" customHeight="1">
       <c r="A18" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C18" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D18" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E18" s="43"/>
       <c r="F18" t="s" s="44">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G18" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J18" s="45">
         <v>41095</v>
@@ -31481,34 +31512,34 @@
       <c r="K18" s="4"/>
       <c r="L18" s="2"/>
       <c r="M18" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" ht="13.75" customHeight="1">
       <c r="A19" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C19" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D19" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E19" s="43"/>
       <c r="F19" t="s" s="44">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G19" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J19" s="45">
         <v>41095</v>
@@ -31516,34 +31547,34 @@
       <c r="K19" s="4"/>
       <c r="L19" s="2"/>
       <c r="M19" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" ht="13.75" customHeight="1">
       <c r="A20" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C20" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D20" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E20" s="43"/>
       <c r="F20" t="s" s="44">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G20" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J20" s="45">
         <v>41095</v>
@@ -31551,34 +31582,34 @@
       <c r="K20" s="4"/>
       <c r="L20" s="2"/>
       <c r="M20" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" ht="13.75" customHeight="1">
       <c r="A21" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C21" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D21" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E21" s="43"/>
       <c r="F21" t="s" s="44">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G21" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J21" s="45">
         <v>41095</v>
@@ -31586,34 +31617,34 @@
       <c r="K21" s="4"/>
       <c r="L21" s="2"/>
       <c r="M21" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" ht="13.75" customHeight="1">
       <c r="A22" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C22" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D22" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E22" s="43"/>
       <c r="F22" t="s" s="44">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G22" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J22" s="45">
         <v>41095</v>
@@ -31621,34 +31652,34 @@
       <c r="K22" s="4"/>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" ht="13.75" customHeight="1">
       <c r="A23" t="s" s="2">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C23" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D23" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E23" s="43"/>
       <c r="F23" t="s" s="44">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G23" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J23" s="45">
         <v>41095</v>
@@ -31656,34 +31687,34 @@
       <c r="K23" s="4"/>
       <c r="L23" s="2"/>
       <c r="M23" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" ht="13.75" customHeight="1">
       <c r="A24" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C24" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D24" t="s" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E24" s="43"/>
       <c r="F24" t="s" s="44">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G24" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J24" s="45">
         <v>41099</v>
@@ -31691,34 +31722,34 @@
       <c r="K24" s="4"/>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" ht="13.75" customHeight="1">
       <c r="A25" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C25" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D25" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E25" s="43"/>
       <c r="F25" t="s" s="44">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G25" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J25" s="45">
         <v>41099</v>
@@ -31726,34 +31757,34 @@
       <c r="K25" s="4"/>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" ht="13.75" customHeight="1">
       <c r="A26" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C26" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D26" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E26" s="43"/>
       <c r="F26" t="s" s="44">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G26" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J26" s="45">
         <v>41099</v>
@@ -31761,34 +31792,34 @@
       <c r="K26" s="4"/>
       <c r="L26" s="2"/>
       <c r="M26" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" ht="13.75" customHeight="1">
       <c r="A27" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C27" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D27" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E27" s="43"/>
       <c r="F27" t="s" s="44">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G27" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J27" s="45">
         <v>41099</v>
@@ -31796,34 +31827,34 @@
       <c r="K27" s="4"/>
       <c r="L27" s="2"/>
       <c r="M27" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" ht="13.75" customHeight="1">
       <c r="A28" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C28" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D28" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E28" s="43"/>
       <c r="F28" t="s" s="44">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G28" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J28" s="45">
         <v>41099</v>
@@ -31831,34 +31862,34 @@
       <c r="K28" s="4"/>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" ht="13.75" customHeight="1">
       <c r="A29" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C29" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D29" t="s" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E29" s="43"/>
       <c r="F29" t="s" s="44">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G29" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J29" s="45">
         <v>41099</v>
@@ -31866,34 +31897,34 @@
       <c r="K29" s="4"/>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" ht="13.75" customHeight="1">
       <c r="A30" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C30" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D30" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E30" s="43"/>
       <c r="F30" t="s" s="44">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G30" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J30" s="45">
         <v>41099</v>
@@ -31901,34 +31932,34 @@
       <c r="K30" s="4"/>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" ht="13.75" customHeight="1">
       <c r="A31" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C31" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D31" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E31" s="43"/>
       <c r="F31" t="s" s="44">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G31" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J31" s="45">
         <v>41099</v>
@@ -31936,34 +31967,34 @@
       <c r="K31" s="4"/>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" ht="13.75" customHeight="1">
       <c r="A32" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C32" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D32" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E32" s="43"/>
       <c r="F32" t="s" s="44">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G32" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J32" s="45">
         <v>41099</v>
@@ -31971,34 +32002,34 @@
       <c r="K32" s="4"/>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" ht="13.75" customHeight="1">
       <c r="A33" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C33" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D33" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E33" s="43"/>
       <c r="F33" t="s" s="44">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G33" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J33" s="45">
         <v>41099</v>
@@ -32006,34 +32037,34 @@
       <c r="K33" s="4"/>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" ht="13.75" customHeight="1">
       <c r="A34" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C34" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D34" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E34" s="43"/>
       <c r="F34" t="s" s="44">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="G34" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J34" s="45">
         <v>41099</v>
@@ -32041,34 +32072,34 @@
       <c r="K34" s="4"/>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" ht="13.75" customHeight="1">
       <c r="A35" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C35" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D35" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E35" s="43"/>
       <c r="F35" t="s" s="44">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G35" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J35" s="45">
         <v>41099</v>
@@ -32076,34 +32107,34 @@
       <c r="K35" s="4"/>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36" ht="13.75" customHeight="1">
       <c r="A36" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C36" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D36" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E36" s="43"/>
       <c r="F36" t="s" s="44">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="G36" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J36" s="45">
         <v>41099</v>
@@ -32111,34 +32142,34 @@
       <c r="K36" s="4"/>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" ht="13.75" customHeight="1">
       <c r="A37" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C37" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D37" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E37" s="43"/>
       <c r="F37" t="s" s="44">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G37" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J37" s="45">
         <v>41099</v>
@@ -32146,34 +32177,34 @@
       <c r="K37" s="4"/>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" ht="13.75" customHeight="1">
       <c r="A38" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C38" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D38" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E38" s="43"/>
       <c r="F38" t="s" s="44">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G38" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J38" s="45">
         <v>41099</v>
@@ -32181,34 +32212,34 @@
       <c r="K38" s="4"/>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" ht="13.75" customHeight="1">
       <c r="A39" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C39" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D39" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E39" s="43"/>
       <c r="F39" t="s" s="44">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G39" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J39" s="45">
         <v>41099</v>
@@ -32216,34 +32247,34 @@
       <c r="K39" s="4"/>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40" ht="13.75" customHeight="1">
       <c r="A40" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C40" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D40" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E40" s="43"/>
       <c r="F40" t="s" s="44">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G40" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J40" s="45">
         <v>41099</v>
@@ -32251,34 +32282,34 @@
       <c r="K40" s="4"/>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="41" ht="13.75" customHeight="1">
       <c r="A41" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C41" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D41" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E41" s="43"/>
       <c r="F41" t="s" s="44">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G41" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J41" s="45">
         <v>41099</v>
@@ -32286,34 +32317,34 @@
       <c r="K41" s="4"/>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42" ht="13.75" customHeight="1">
       <c r="A42" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C42" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D42" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E42" s="43"/>
       <c r="F42" t="s" s="44">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G42" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J42" s="45">
         <v>41100</v>
@@ -32321,34 +32352,34 @@
       <c r="K42" s="4"/>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="43" ht="13.75" customHeight="1">
       <c r="A43" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C43" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D43" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E43" s="43"/>
       <c r="F43" t="s" s="44">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G43" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J43" s="45">
         <v>41100</v>
@@ -32356,34 +32387,34 @@
       <c r="K43" s="4"/>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44" ht="13.75" customHeight="1">
       <c r="A44" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C44" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D44" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E44" s="43"/>
       <c r="F44" t="s" s="44">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G44" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J44" s="45">
         <v>41100</v>
@@ -32391,34 +32422,34 @@
       <c r="K44" s="4"/>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45" ht="13.75" customHeight="1">
       <c r="A45" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C45" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D45" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E45" s="43"/>
       <c r="F45" t="s" s="44">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G45" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J45" s="45">
         <v>41100</v>
@@ -32426,34 +32457,34 @@
       <c r="K45" s="4"/>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46" ht="13.75" customHeight="1">
       <c r="A46" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C46" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D46" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E46" s="43"/>
       <c r="F46" t="s" s="44">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G46" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J46" s="45">
         <v>41100</v>
@@ -32461,34 +32492,34 @@
       <c r="K46" s="4"/>
       <c r="L46" s="2"/>
       <c r="M46" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="47" ht="13.75" customHeight="1">
       <c r="A47" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C47" t="s" s="3">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D47" t="s" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E47" s="43"/>
       <c r="F47" t="s" s="44">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G47" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J47" s="45">
         <v>41100</v>
@@ -32496,34 +32527,34 @@
       <c r="K47" s="4"/>
       <c r="L47" s="2"/>
       <c r="M47" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48" ht="13.75" customHeight="1">
       <c r="A48" t="s" s="16">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B48" t="s" s="16">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C48" t="s" s="46">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D48" t="s" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E48" s="43"/>
       <c r="F48" t="s" s="44">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G48" t="s" s="13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>7</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J48" s="45">
         <v>41081</v>
@@ -32531,22 +32562,22 @@
       <c r="K48" s="4"/>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="49" ht="14.7" customHeight="1">
       <c r="A49" t="s" s="47">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B49" s="36"/>
       <c r="C49" t="s" s="48">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D49" s="49"/>
       <c r="E49" s="4"/>
       <c r="F49" s="30"/>
       <c r="G49" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>7</v>
@@ -32558,22 +32589,22 @@
       <c r="K49" s="4"/>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50" ht="14.7" customHeight="1">
       <c r="A50" t="s" s="47">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B50" s="36"/>
       <c r="C50" t="s" s="48">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D50" s="49"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="G50" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>7</v>
@@ -32585,22 +32616,22 @@
       <c r="K50" s="4"/>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="51" ht="14.7" customHeight="1">
       <c r="A51" t="s" s="47">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B51" s="36"/>
       <c r="C51" t="s" s="48">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D51" s="49"/>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
       <c r="G51" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>7</v>
@@ -32612,22 +32643,22 @@
       <c r="K51" s="4"/>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52" ht="14.7" customHeight="1">
       <c r="A52" t="s" s="47">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B52" s="36"/>
       <c r="C52" t="s" s="48">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D52" s="49"/>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
       <c r="G52" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>7</v>
@@ -32639,22 +32670,22 @@
       <c r="K52" s="4"/>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="53" ht="14.7" customHeight="1">
       <c r="A53" t="s" s="47">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B53" s="36"/>
       <c r="C53" t="s" s="48">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D53" s="49"/>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
       <c r="G53" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>7</v>
@@ -32666,22 +32697,22 @@
       <c r="K53" s="4"/>
       <c r="L53" s="2"/>
       <c r="M53" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54" ht="14.7" customHeight="1">
       <c r="A54" t="s" s="47">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B54" s="36"/>
       <c r="C54" t="s" s="48">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D54" s="49"/>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
       <c r="G54" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>7</v>
@@ -32693,22 +32724,22 @@
       <c r="K54" s="4"/>
       <c r="L54" s="2"/>
       <c r="M54" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="55" ht="14.7" customHeight="1">
       <c r="A55" t="s" s="47">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B55" s="36"/>
       <c r="C55" t="s" s="48">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D55" s="49"/>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
       <c r="G55" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>7</v>
@@ -32720,22 +32751,22 @@
       <c r="K55" s="4"/>
       <c r="L55" s="2"/>
       <c r="M55" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="56" ht="14.7" customHeight="1">
       <c r="A56" t="s" s="47">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B56" s="36"/>
       <c r="C56" t="s" s="48">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D56" s="49"/>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
       <c r="G56" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>7</v>
@@ -32747,22 +32778,22 @@
       <c r="K56" s="4"/>
       <c r="L56" s="2"/>
       <c r="M56" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57" ht="14.7" customHeight="1">
       <c r="A57" t="s" s="47">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B57" s="36"/>
       <c r="C57" t="s" s="48">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D57" s="49"/>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
       <c r="G57" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>7</v>
@@ -32774,22 +32805,22 @@
       <c r="K57" s="4"/>
       <c r="L57" s="2"/>
       <c r="M57" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58" ht="14.7" customHeight="1">
       <c r="A58" t="s" s="47">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B58" s="36"/>
       <c r="C58" t="s" s="48">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D58" s="49"/>
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
       <c r="G58" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>7</v>
@@ -32801,22 +32832,22 @@
       <c r="K58" s="4"/>
       <c r="L58" s="2"/>
       <c r="M58" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="59" ht="13.65" customHeight="1">
       <c r="A59" t="s" s="47">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B59" s="36"/>
       <c r="C59" t="s" s="48">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D59" s="49"/>
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
       <c r="G59" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>7</v>
@@ -32828,22 +32859,22 @@
       <c r="K59" s="4"/>
       <c r="L59" s="2"/>
       <c r="M59" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60" ht="13.65" customHeight="1">
       <c r="A60" t="s" s="47">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B60" s="36"/>
       <c r="C60" t="s" s="48">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D60" s="49"/>
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
       <c r="G60" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>7</v>
@@ -32855,22 +32886,22 @@
       <c r="K60" s="4"/>
       <c r="L60" s="2"/>
       <c r="M60" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="61" ht="13.65" customHeight="1">
       <c r="A61" t="s" s="39">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B61" s="38"/>
       <c r="C61" t="s" s="39">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
       <c r="G61" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>7</v>
@@ -32882,22 +32913,22 @@
       <c r="K61" s="4"/>
       <c r="L61" s="2"/>
       <c r="M61" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="62" ht="13.65" customHeight="1">
       <c r="A62" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
       <c r="G62" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>7</v>
@@ -32909,22 +32940,22 @@
       <c r="K62" s="4"/>
       <c r="L62" s="2"/>
       <c r="M62" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63" ht="13.65" customHeight="1">
       <c r="A63" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="F63" s="4"/>
       <c r="G63" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>7</v>
@@ -32936,22 +32967,22 @@
       <c r="K63" s="4"/>
       <c r="L63" s="2"/>
       <c r="M63" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="64" ht="13.65" customHeight="1">
       <c r="A64" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
       <c r="G64" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>7</v>
@@ -32963,22 +32994,22 @@
       <c r="K64" s="4"/>
       <c r="L64" s="2"/>
       <c r="M64" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" ht="13.65" customHeight="1">
       <c r="A65" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B65" s="4"/>
       <c r="C65" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
       <c r="G65" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>7</v>
@@ -32990,22 +33021,22 @@
       <c r="K65" s="4"/>
       <c r="L65" s="2"/>
       <c r="M65" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66" ht="13.65" customHeight="1">
       <c r="A66" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B66" s="4"/>
       <c r="C66" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
       <c r="G66" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>7</v>
@@ -33017,22 +33048,22 @@
       <c r="K66" s="4"/>
       <c r="L66" s="2"/>
       <c r="M66" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="67" ht="13.65" customHeight="1">
       <c r="A67" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B67" s="4"/>
       <c r="C67" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
       <c r="G67" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>7</v>
@@ -33044,22 +33075,22 @@
       <c r="K67" s="4"/>
       <c r="L67" s="2"/>
       <c r="M67" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68" ht="13.65" customHeight="1">
       <c r="A68" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
       <c r="G68" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>7</v>
@@ -33071,22 +33102,22 @@
       <c r="K68" s="4"/>
       <c r="L68" s="2"/>
       <c r="M68" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="69" ht="13.65" customHeight="1">
       <c r="A69" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
       <c r="G69" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>7</v>
@@ -33098,22 +33129,22 @@
       <c r="K69" s="4"/>
       <c r="L69" s="2"/>
       <c r="M69" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70" ht="13.65" customHeight="1">
       <c r="A70" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
       <c r="F70" s="4"/>
       <c r="G70" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>7</v>
@@ -33125,22 +33156,22 @@
       <c r="K70" s="4"/>
       <c r="L70" s="2"/>
       <c r="M70" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="71" ht="13.65" customHeight="1">
       <c r="A71" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
       <c r="G71" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>7</v>
@@ -33152,22 +33183,22 @@
       <c r="K71" s="4"/>
       <c r="L71" s="2"/>
       <c r="M71" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="72" ht="13.65" customHeight="1">
       <c r="A72" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
       <c r="G72" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>7</v>
@@ -33179,22 +33210,22 @@
       <c r="K72" s="4"/>
       <c r="L72" s="2"/>
       <c r="M72" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="73" ht="13.65" customHeight="1">
       <c r="A73" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
       <c r="G73" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>7</v>
@@ -33206,22 +33237,22 @@
       <c r="K73" s="4"/>
       <c r="L73" s="2"/>
       <c r="M73" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="74" ht="13.65" customHeight="1">
       <c r="A74" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
       <c r="G74" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>7</v>
@@ -33233,22 +33264,22 @@
       <c r="K74" s="4"/>
       <c r="L74" s="2"/>
       <c r="M74" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="75" ht="13.65" customHeight="1">
       <c r="A75" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B75" s="4"/>
       <c r="C75" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
       <c r="F75" s="4"/>
       <c r="G75" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>7</v>
@@ -33260,22 +33291,22 @@
       <c r="K75" s="4"/>
       <c r="L75" s="2"/>
       <c r="M75" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="76" ht="13.65" customHeight="1">
       <c r="A76" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B76" s="4"/>
       <c r="C76" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
       <c r="F76" s="4"/>
       <c r="G76" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>7</v>
@@ -33287,22 +33318,22 @@
       <c r="K76" s="4"/>
       <c r="L76" s="2"/>
       <c r="M76" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="77" ht="13.65" customHeight="1">
       <c r="A77" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B77" s="4"/>
       <c r="C77" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
       <c r="F77" s="4"/>
       <c r="G77" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>7</v>
@@ -33314,22 +33345,22 @@
       <c r="K77" s="4"/>
       <c r="L77" s="2"/>
       <c r="M77" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="78" ht="13.65" customHeight="1">
       <c r="A78" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B78" s="4"/>
       <c r="C78" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
       <c r="F78" s="4"/>
       <c r="G78" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>7</v>
@@ -33341,22 +33372,22 @@
       <c r="K78" s="4"/>
       <c r="L78" s="2"/>
       <c r="M78" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="79" ht="13.65" customHeight="1">
       <c r="A79" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B79" s="4"/>
       <c r="C79" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
       <c r="F79" s="4"/>
       <c r="G79" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>7</v>
@@ -33368,22 +33399,22 @@
       <c r="K79" s="4"/>
       <c r="L79" s="2"/>
       <c r="M79" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="80" ht="13.65" customHeight="1">
       <c r="A80" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B80" s="4"/>
       <c r="C80" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
       <c r="F80" s="4"/>
       <c r="G80" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>7</v>
@@ -33395,7 +33426,7 @@
       <c r="K80" s="4"/>
       <c r="L80" s="2"/>
       <c r="M80" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="81" ht="13.65" customHeight="1">
@@ -47376,103 +47407,103 @@
         <v>2</v>
       </c>
       <c r="B1" t="s" s="16">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C1" t="s" s="16">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D1" t="s" s="16">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E1" t="s" s="16">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F1" t="s" s="16">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="G1" t="s" s="16">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="H1" t="s" s="16">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" ht="14.7" customHeight="1">
       <c r="A2" t="s" s="47">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B2" t="s" s="51">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C2" t="s" s="34">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D2" t="s" s="51">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="E2" t="s" s="34">
         <v>7</v>
       </c>
       <c r="F2" t="s" s="48">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="G2" t="s" s="48">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="H2" t="s" s="34">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" ht="14.7" customHeight="1">
       <c r="A3" t="s" s="47">
+        <v>277</v>
+      </c>
+      <c r="B3" t="s" s="51">
         <v>273</v>
       </c>
-      <c r="B3" t="s" s="51">
-        <v>269</v>
-      </c>
       <c r="C3" t="s" s="51">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D3" t="s" s="51">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="E3" t="s" s="34">
         <v>7</v>
       </c>
       <c r="F3" t="s" s="48">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="G3" t="s" s="48">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="H3" t="s" s="34">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" ht="14.7" customHeight="1">
       <c r="A4" t="s" s="47">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B4" t="s" s="51">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C4" t="s" s="51">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D4" t="s" s="51">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="E4" t="s" s="34">
         <v>7</v>
       </c>
       <c r="F4" t="s" s="48">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="G4" t="s" s="48">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="H4" t="s" s="34">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5" ht="13.65" customHeight="1">
@@ -56934,10 +56965,10 @@
   <sheetData>
     <row r="1" ht="13.2" customHeight="1">
       <c r="A1" t="s" s="53">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B1" t="s" s="53">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C1" s="54"/>
       <c r="D1" s="54"/>
@@ -56945,10 +56976,10 @@
     </row>
     <row r="2" ht="13.2" customHeight="1">
       <c r="A2" t="s" s="55">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B2" t="s" s="56">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C2" s="57"/>
       <c r="D2" s="57"/>
@@ -56956,10 +56987,10 @@
     </row>
     <row r="3" ht="13" customHeight="1">
       <c r="A3" t="s" s="58">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B3" t="s" s="59">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C3" s="60"/>
       <c r="D3" s="60"/>
@@ -56967,10 +56998,10 @@
     </row>
     <row r="4" ht="13" customHeight="1">
       <c r="A4" t="s" s="58">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B4" t="s" s="59">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C4" s="60"/>
       <c r="D4" s="60"/>
@@ -56978,10 +57009,10 @@
     </row>
     <row r="5" ht="13" customHeight="1">
       <c r="A5" t="s" s="61">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B5" t="s" s="62">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C5" s="60"/>
       <c r="D5" s="60"/>
@@ -56989,10 +57020,10 @@
     </row>
     <row r="6" ht="13" customHeight="1">
       <c r="A6" t="s" s="58">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B6" t="s" s="61">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C6" s="60"/>
       <c r="D6" s="60"/>
@@ -57000,10 +57031,10 @@
     </row>
     <row r="7" ht="13" customHeight="1">
       <c r="A7" t="s" s="58">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B7" t="s" s="59">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C7" s="60"/>
       <c r="D7" s="60"/>
@@ -57011,10 +57042,10 @@
     </row>
     <row r="8" ht="13" customHeight="1">
       <c r="A8" t="s" s="58">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B8" t="s" s="59">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C8" s="60"/>
       <c r="D8" s="60"/>
@@ -57022,10 +57053,10 @@
     </row>
     <row r="9" ht="13" customHeight="1">
       <c r="A9" t="s" s="58">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B9" t="s" s="59">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C9" s="60"/>
       <c r="D9" s="60"/>
@@ -57033,10 +57064,10 @@
     </row>
     <row r="10" ht="13" customHeight="1">
       <c r="A10" t="s" s="58">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B10" t="s" s="59">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C10" s="60"/>
       <c r="D10" s="60"/>
@@ -57044,10 +57075,10 @@
     </row>
     <row r="11" ht="13" customHeight="1">
       <c r="A11" t="s" s="58">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B11" t="s" s="59">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C11" s="60"/>
       <c r="D11" s="60"/>
@@ -57055,10 +57086,10 @@
     </row>
     <row r="12" ht="13" customHeight="1">
       <c r="A12" t="s" s="58">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B12" t="s" s="59">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C12" s="60"/>
       <c r="D12" s="60"/>
@@ -57066,10 +57097,10 @@
     </row>
     <row r="13" ht="13" customHeight="1">
       <c r="A13" t="s" s="58">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B13" t="s" s="59">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C13" s="60"/>
       <c r="D13" s="60"/>
@@ -57077,10 +57108,10 @@
     </row>
     <row r="14" ht="13" customHeight="1">
       <c r="A14" t="s" s="58">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B14" t="s" s="59">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C14" s="60"/>
       <c r="D14" s="60"/>
@@ -57088,10 +57119,10 @@
     </row>
     <row r="15" ht="13" customHeight="1">
       <c r="A15" t="s" s="58">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B15" t="s" s="59">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C15" s="60"/>
       <c r="D15" s="60"/>
@@ -57099,10 +57130,10 @@
     </row>
     <row r="16" ht="13" customHeight="1">
       <c r="A16" t="s" s="58">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B16" t="s" s="59">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C16" s="60"/>
       <c r="D16" s="60"/>
@@ -57110,10 +57141,10 @@
     </row>
     <row r="17" ht="13" customHeight="1">
       <c r="A17" t="s" s="58">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B17" t="s" s="59">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C17" s="60"/>
       <c r="D17" s="60"/>
@@ -57121,10 +57152,10 @@
     </row>
     <row r="18" ht="13" customHeight="1">
       <c r="A18" t="s" s="58">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B18" t="s" s="59">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C18" s="60"/>
       <c r="D18" s="60"/>
@@ -57132,10 +57163,10 @@
     </row>
     <row r="19" ht="13" customHeight="1">
       <c r="A19" t="s" s="58">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B19" t="s" s="59">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C19" s="60"/>
       <c r="D19" s="60"/>
@@ -57143,10 +57174,10 @@
     </row>
     <row r="20" ht="13" customHeight="1">
       <c r="A20" t="s" s="58">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B20" t="s" s="59">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C20" s="60"/>
       <c r="D20" s="60"/>
@@ -57154,10 +57185,10 @@
     </row>
     <row r="21" ht="13" customHeight="1">
       <c r="A21" t="s" s="58">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s" s="59">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C21" s="60"/>
       <c r="D21" s="60"/>
@@ -57165,10 +57196,10 @@
     </row>
     <row r="22" ht="13" customHeight="1">
       <c r="A22" t="s" s="58">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s" s="59">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C22" s="60"/>
       <c r="D22" s="60"/>
@@ -57176,10 +57207,10 @@
     </row>
     <row r="23" ht="13" customHeight="1">
       <c r="A23" t="s" s="58">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s" s="59">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C23" s="60"/>
       <c r="D23" s="60"/>
@@ -57187,10 +57218,10 @@
     </row>
     <row r="24" ht="13" customHeight="1">
       <c r="A24" t="s" s="58">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B24" t="s" s="59">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C24" s="60"/>
       <c r="D24" s="60"/>
@@ -57198,10 +57229,10 @@
     </row>
     <row r="25" ht="13" customHeight="1">
       <c r="A25" t="s" s="58">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B25" t="s" s="59">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C25" s="60"/>
       <c r="D25" s="60"/>
@@ -57209,10 +57240,10 @@
     </row>
     <row r="26" ht="13" customHeight="1">
       <c r="A26" t="s" s="58">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B26" t="s" s="59">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C26" s="60"/>
       <c r="D26" s="60"/>
@@ -57220,10 +57251,10 @@
     </row>
     <row r="27" ht="13" customHeight="1">
       <c r="A27" t="s" s="58">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B27" t="s" s="59">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C27" s="60"/>
       <c r="D27" s="60"/>
@@ -57231,10 +57262,10 @@
     </row>
     <row r="28" ht="13" customHeight="1">
       <c r="A28" t="s" s="58">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B28" t="s" s="59">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C28" s="60"/>
       <c r="D28" s="60"/>
@@ -57242,10 +57273,10 @@
     </row>
     <row r="29" ht="13" customHeight="1">
       <c r="A29" t="s" s="58">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B29" t="s" s="59">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C29" s="60"/>
       <c r="D29" s="60"/>
@@ -57253,10 +57284,10 @@
     </row>
     <row r="30" ht="13" customHeight="1">
       <c r="A30" t="s" s="58">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B30" t="s" s="59">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C30" s="60"/>
       <c r="D30" s="60"/>
@@ -57264,10 +57295,10 @@
     </row>
     <row r="31" ht="13" customHeight="1">
       <c r="A31" t="s" s="58">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B31" t="s" s="59">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C31" s="60"/>
       <c r="D31" s="60"/>
@@ -57275,10 +57306,10 @@
     </row>
     <row r="32" ht="13" customHeight="1">
       <c r="A32" t="s" s="58">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B32" t="s" s="59">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C32" s="60"/>
       <c r="D32" s="60"/>
@@ -57286,10 +57317,10 @@
     </row>
     <row r="33" ht="13" customHeight="1">
       <c r="A33" t="s" s="58">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B33" t="s" s="59">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C33" s="60"/>
       <c r="D33" s="60"/>
@@ -57297,10 +57328,10 @@
     </row>
     <row r="34" ht="13" customHeight="1">
       <c r="A34" t="s" s="58">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B34" t="s" s="59">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C34" s="60"/>
       <c r="D34" s="60"/>
@@ -57308,10 +57339,10 @@
     </row>
     <row r="35" ht="13" customHeight="1">
       <c r="A35" t="s" s="58">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B35" t="s" s="59">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C35" s="60"/>
       <c r="D35" s="60"/>
@@ -57319,10 +57350,10 @@
     </row>
     <row r="36" ht="13" customHeight="1">
       <c r="A36" t="s" s="58">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B36" t="s" s="59">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C36" s="60"/>
       <c r="D36" s="60"/>
@@ -57330,10 +57361,10 @@
     </row>
     <row r="37" ht="13" customHeight="1">
       <c r="A37" t="s" s="58">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B37" t="s" s="59">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C37" s="60"/>
       <c r="D37" s="60"/>
@@ -57341,10 +57372,10 @@
     </row>
     <row r="38" ht="13" customHeight="1">
       <c r="A38" t="s" s="58">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B38" t="s" s="59">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C38" s="60"/>
       <c r="D38" s="60"/>
@@ -57352,10 +57383,10 @@
     </row>
     <row r="39" ht="13" customHeight="1">
       <c r="A39" t="s" s="58">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B39" t="s" s="59">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C39" s="60"/>
       <c r="D39" s="60"/>
@@ -57363,10 +57394,10 @@
     </row>
     <row r="40" ht="13" customHeight="1">
       <c r="A40" t="s" s="58">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B40" t="s" s="59">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C40" s="60"/>
       <c r="D40" s="60"/>
@@ -57374,10 +57405,10 @@
     </row>
     <row r="41" ht="13" customHeight="1">
       <c r="A41" t="s" s="58">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B41" t="s" s="59">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C41" s="60"/>
       <c r="D41" s="60"/>
@@ -57385,10 +57416,10 @@
     </row>
     <row r="42" ht="13" customHeight="1">
       <c r="A42" t="s" s="58">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B42" t="s" s="59">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C42" s="60"/>
       <c r="D42" s="60"/>
@@ -57396,10 +57427,10 @@
     </row>
     <row r="43" ht="13" customHeight="1">
       <c r="A43" t="s" s="58">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B43" t="s" s="59">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C43" s="60"/>
       <c r="D43" s="60"/>
@@ -57407,10 +57438,10 @@
     </row>
     <row r="44" ht="13" customHeight="1">
       <c r="A44" t="s" s="58">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B44" t="s" s="59">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C44" s="60"/>
       <c r="D44" s="60"/>
@@ -57418,10 +57449,10 @@
     </row>
     <row r="45" ht="13" customHeight="1">
       <c r="A45" t="s" s="58">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B45" t="s" s="59">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C45" s="60"/>
       <c r="D45" s="60"/>
@@ -57429,10 +57460,10 @@
     </row>
     <row r="46" ht="13" customHeight="1">
       <c r="A46" t="s" s="58">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B46" t="s" s="59">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C46" s="60"/>
       <c r="D46" s="60"/>
@@ -57440,10 +57471,10 @@
     </row>
     <row r="47" ht="13" customHeight="1">
       <c r="A47" t="s" s="58">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B47" t="s" s="59">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C47" s="60"/>
       <c r="D47" s="60"/>
@@ -57451,10 +57482,10 @@
     </row>
     <row r="48" ht="13" customHeight="1">
       <c r="A48" t="s" s="63">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B48" t="s" s="59">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C48" s="60"/>
       <c r="D48" s="60"/>
@@ -57462,10 +57493,10 @@
     </row>
     <row r="49" ht="13" customHeight="1">
       <c r="A49" t="s" s="39">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B49" t="s" s="64">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C49" s="60"/>
       <c r="D49" s="60"/>
@@ -57473,10 +57504,10 @@
     </row>
     <row r="50" ht="13" customHeight="1">
       <c r="A50" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B50" t="s" s="64">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C50" s="60"/>
       <c r="D50" s="60"/>
@@ -57484,10 +57515,10 @@
     </row>
     <row r="51" ht="13" customHeight="1">
       <c r="A51" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B51" t="s" s="64">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C51" s="60"/>
       <c r="D51" s="60"/>
@@ -57495,10 +57526,10 @@
     </row>
     <row r="52" ht="13" customHeight="1">
       <c r="A52" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B52" t="s" s="64">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C52" s="60"/>
       <c r="D52" s="60"/>
@@ -57506,10 +57537,10 @@
     </row>
     <row r="53" ht="13" customHeight="1">
       <c r="A53" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B53" t="s" s="64">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C53" s="60"/>
       <c r="D53" s="60"/>
@@ -57517,10 +57548,10 @@
     </row>
     <row r="54" ht="13" customHeight="1">
       <c r="A54" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B54" t="s" s="64">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C54" s="60"/>
       <c r="D54" s="60"/>
@@ -57528,10 +57559,10 @@
     </row>
     <row r="55" ht="13" customHeight="1">
       <c r="A55" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B55" t="s" s="64">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C55" s="60"/>
       <c r="D55" s="60"/>
@@ -57539,10 +57570,10 @@
     </row>
     <row r="56" ht="13" customHeight="1">
       <c r="A56" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B56" t="s" s="64">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C56" s="60"/>
       <c r="D56" s="60"/>
@@ -57550,10 +57581,10 @@
     </row>
     <row r="57" ht="13" customHeight="1">
       <c r="A57" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B57" t="s" s="64">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C57" s="60"/>
       <c r="D57" s="60"/>
@@ -57561,10 +57592,10 @@
     </row>
     <row r="58" ht="13" customHeight="1">
       <c r="A58" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B58" t="s" s="64">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C58" s="60"/>
       <c r="D58" s="60"/>
@@ -57572,10 +57603,10 @@
     </row>
     <row r="59" ht="13" customHeight="1">
       <c r="A59" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B59" t="s" s="64">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C59" s="60"/>
       <c r="D59" s="60"/>
@@ -57583,10 +57614,10 @@
     </row>
     <row r="60" ht="13" customHeight="1">
       <c r="A60" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B60" t="s" s="64">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C60" s="60"/>
       <c r="D60" s="60"/>
@@ -57594,10 +57625,10 @@
     </row>
     <row r="61" ht="13" customHeight="1">
       <c r="A61" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B61" t="s" s="64">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C61" s="60"/>
       <c r="D61" s="60"/>
@@ -57605,10 +57636,10 @@
     </row>
     <row r="62" ht="13" customHeight="1">
       <c r="A62" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B62" t="s" s="64">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C62" s="60"/>
       <c r="D62" s="60"/>
@@ -57616,10 +57647,10 @@
     </row>
     <row r="63" ht="13" customHeight="1">
       <c r="A63" t="s" s="16">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B63" t="s" s="64">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C63" s="60"/>
       <c r="D63" s="60"/>
@@ -57627,10 +57658,10 @@
     </row>
     <row r="64" ht="13" customHeight="1">
       <c r="A64" t="s" s="39">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B64" t="s" s="65">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C64" s="60"/>
       <c r="D64" s="60"/>
@@ -57638,10 +57669,10 @@
     </row>
     <row r="65" ht="13" customHeight="1">
       <c r="A65" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C65" s="66"/>
       <c r="D65" s="60"/>
@@ -57649,10 +57680,10 @@
     </row>
     <row r="66" ht="13" customHeight="1">
       <c r="A66" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C66" s="66"/>
       <c r="D66" s="60"/>
@@ -57660,10 +57691,10 @@
     </row>
     <row r="67" ht="13" customHeight="1">
       <c r="A67" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C67" s="66"/>
       <c r="D67" s="60"/>
@@ -57671,10 +57702,10 @@
     </row>
     <row r="68" ht="13" customHeight="1">
       <c r="A68" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C68" s="66"/>
       <c r="D68" s="60"/>
@@ -57682,10 +57713,10 @@
     </row>
     <row r="69" ht="13" customHeight="1">
       <c r="A69" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C69" s="66"/>
       <c r="D69" s="60"/>
@@ -57693,10 +57724,10 @@
     </row>
     <row r="70" ht="13" customHeight="1">
       <c r="A70" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="C70" s="66"/>
       <c r="D70" s="60"/>
@@ -57704,10 +57735,10 @@
     </row>
     <row r="71" ht="13" customHeight="1">
       <c r="A71" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C71" s="66"/>
       <c r="D71" s="60"/>
@@ -57715,10 +57746,10 @@
     </row>
     <row r="72" ht="13" customHeight="1">
       <c r="A72" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C72" s="66"/>
       <c r="D72" s="60"/>
@@ -57758,1002 +57789,1002 @@
   <sheetData>
     <row r="1" ht="13.2" customHeight="1">
       <c r="A1" t="s" s="68">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B1" t="s" s="69">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C1" t="s" s="70">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D1" t="s" s="53">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E1" t="s" s="53">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="F1" t="s" s="53">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2" ht="13.2" customHeight="1">
       <c r="A2" t="s" s="71">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B2" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C2" t="s" s="72">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D2" t="s" s="73">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E2" t="s" s="73">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F2" t="s" s="74">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3" ht="13" customHeight="1">
       <c r="A3" t="s" s="71">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B3" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C3" t="s" s="72">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D3" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E3" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F3" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" ht="13" customHeight="1">
       <c r="A4" t="s" s="71">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B4" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C4" t="s" s="72">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D4" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E4" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F4" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" ht="13" customHeight="1">
       <c r="A5" t="s" s="71">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B5" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C5" t="s" s="72">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D5" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E5" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F5" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6" ht="13" customHeight="1">
       <c r="A6" t="s" s="71">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B6" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C6" t="s" s="72">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D6" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E6" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F6" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" ht="13" customHeight="1">
       <c r="A7" t="s" s="71">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B7" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C7" t="s" s="72">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D7" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E7" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F7" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" ht="13" customHeight="1">
       <c r="A8" t="s" s="71">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C8" t="s" s="72">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D8" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E8" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F8" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1">
       <c r="A9" t="s" s="71">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B9" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C9" t="s" s="72">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D9" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E9" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F9" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1">
       <c r="A10" t="s" s="71">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B10" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C10" t="s" s="72">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D10" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E10" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F10" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11" ht="13" customHeight="1">
       <c r="A11" t="s" s="71">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B11" t="s" s="72">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C11" t="s" s="72">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D11" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E11" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F11" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1">
       <c r="A12" t="s" s="71">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B12" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C12" t="s" s="72">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D12" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E12" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F12" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13" ht="13" customHeight="1">
       <c r="A13" t="s" s="71">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B13" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C13" t="s" s="72">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D13" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E13" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F13" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14" ht="13" customHeight="1">
       <c r="A14" t="s" s="71">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B14" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C14" t="s" s="72">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D14" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E14" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F14" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1">
       <c r="A15" t="s" s="71">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C15" t="s" s="72">
+        <v>297</v>
+      </c>
+      <c r="D15" t="s" s="75">
         <v>293</v>
       </c>
-      <c r="D15" t="s" s="75">
-        <v>289</v>
-      </c>
       <c r="E15" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F15" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1">
       <c r="A16" t="s" s="71">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B16" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C16" t="s" s="72">
+        <v>298</v>
+      </c>
+      <c r="D16" t="s" s="75">
+        <v>293</v>
+      </c>
+      <c r="E16" t="s" s="75">
         <v>294</v>
       </c>
-      <c r="D16" t="s" s="75">
-        <v>289</v>
-      </c>
-      <c r="E16" t="s" s="75">
-        <v>290</v>
-      </c>
       <c r="F16" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1">
       <c r="A17" t="s" s="71">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B17" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C17" t="s" s="72">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D17" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E17" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F17" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="18" ht="13" customHeight="1">
       <c r="A18" t="s" s="71">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B18" t="s" s="72">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C18" t="s" s="72">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D18" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E18" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F18" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19" ht="13" customHeight="1">
       <c r="A19" t="s" s="71">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B19" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C19" t="s" s="72">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D19" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E19" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F19" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="20" ht="13" customHeight="1">
       <c r="A20" t="s" s="71">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B20" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C20" t="s" s="72">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D20" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E20" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F20" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="21" ht="13" customHeight="1">
       <c r="A21" t="s" s="71">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B21" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C21" t="s" s="72">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="D21" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E21" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F21" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="22" ht="13" customHeight="1">
       <c r="A22" t="s" s="71">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B22" t="s" s="72">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C22" t="s" s="72">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D22" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E22" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F22" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="23" ht="13" customHeight="1">
       <c r="A23" t="s" s="71">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B23" t="s" s="72">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C23" t="s" s="72">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D23" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E23" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F23" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="24" ht="13" customHeight="1">
       <c r="A24" t="s" s="71">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B24" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C24" t="s" s="72">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D24" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E24" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F24" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25" ht="13" customHeight="1">
       <c r="A25" t="s" s="71">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B25" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C25" t="s" s="72">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D25" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E25" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F25" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="26" ht="13" customHeight="1">
       <c r="A26" t="s" s="71">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B26" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C26" t="s" s="72">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D26" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E26" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F26" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" ht="13" customHeight="1">
       <c r="A27" t="s" s="71">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B27" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C27" t="s" s="72">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D27" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E27" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F27" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" ht="13" customHeight="1">
       <c r="A28" t="s" s="71">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B28" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C28" t="s" s="72">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D28" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E28" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F28" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" ht="13" customHeight="1">
       <c r="A29" t="s" s="71">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B29" t="s" s="72">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C29" t="s" s="72">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D29" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E29" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F29" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" ht="13" customHeight="1">
       <c r="A30" t="s" s="71">
+        <v>132</v>
+      </c>
+      <c r="B30" t="s" s="72">
+        <v>295</v>
+      </c>
+      <c r="C30" t="s" s="72">
         <v>128</v>
       </c>
-      <c r="B30" t="s" s="72">
-        <v>291</v>
-      </c>
-      <c r="C30" t="s" s="72">
-        <v>124</v>
-      </c>
       <c r="D30" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E30" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F30" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" ht="13" customHeight="1">
       <c r="A31" t="s" s="71">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B31" t="s" s="72">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C31" t="s" s="72">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D31" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E31" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F31" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" ht="13" customHeight="1">
       <c r="A32" t="s" s="71">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B32" t="s" s="72">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C32" t="s" s="72">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D32" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E32" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F32" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" ht="13" customHeight="1">
       <c r="A33" t="s" s="71">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B33" t="s" s="72">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C33" t="s" s="72">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D33" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E33" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F33" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" ht="13" customHeight="1">
       <c r="A34" t="s" s="71">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B34" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C34" t="s" s="72">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D34" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E34" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F34" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" ht="13" customHeight="1">
       <c r="A35" t="s" s="71">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B35" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C35" t="s" s="72">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D35" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E35" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F35" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36" ht="13" customHeight="1">
       <c r="A36" t="s" s="71">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B36" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C36" t="s" s="72">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D36" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E36" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F36" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="37" ht="13" customHeight="1">
       <c r="A37" t="s" s="71">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B37" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C37" t="s" s="72">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D37" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E37" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F37" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="38" ht="13" customHeight="1">
       <c r="A38" t="s" s="71">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B38" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C38" t="s" s="72">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D38" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E38" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F38" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="39" ht="13" customHeight="1">
       <c r="A39" t="s" s="71">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B39" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C39" t="s" s="72">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D39" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E39" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F39" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="40" ht="13" customHeight="1">
       <c r="A40" t="s" s="71">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B40" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C40" t="s" s="72">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D40" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E40" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F40" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="41" ht="13" customHeight="1">
       <c r="A41" t="s" s="71">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B41" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C41" t="s" s="72">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D41" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E41" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F41" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="42" ht="13" customHeight="1">
       <c r="A42" t="s" s="71">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B42" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C42" t="s" s="72">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D42" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E42" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F42" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="43" ht="13" customHeight="1">
       <c r="A43" t="s" s="71">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B43" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C43" t="s" s="72">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D43" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E43" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F43" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="44" ht="13" customHeight="1">
       <c r="A44" t="s" s="71">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B44" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C44" t="s" s="72">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D44" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E44" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F44" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="45" ht="13" customHeight="1">
       <c r="A45" t="s" s="71">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B45" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C45" t="s" s="72">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D45" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E45" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F45" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="46" ht="13" customHeight="1">
       <c r="A46" t="s" s="71">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B46" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C46" t="s" s="72">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D46" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E46" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F46" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="47" ht="13" customHeight="1">
       <c r="A47" t="s" s="71">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B47" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C47" t="s" s="72">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D47" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E47" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F47" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="48" ht="13" customHeight="1">
       <c r="A48" t="s" s="71">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B48" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C48" t="s" s="72">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D48" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E48" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F48" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="49" ht="13" customHeight="1">
       <c r="A49" t="s" s="71">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B49" t="s" s="72">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C49" t="s" s="72">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D49" t="s" s="75">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E49" t="s" s="75">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F49" t="s" s="76">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="50" ht="13" customHeight="1">
       <c r="A50" t="s" s="77">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B50" t="s" s="78">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C50" t="s" s="78">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="D50" t="s" s="79">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E50" t="s" s="79">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F50" t="s" s="80">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/datasets/Import_Chartres.xlsx
+++ b/src/main/resources/datasets/Import_Chartres.xlsx
@@ -93,7 +93,7 @@
     </r>
   </si>
   <si>
-    <t>Test th230</t>
+    <t>Test th252</t>
   </si>
   <si>
     <t>Astuce pour importer le thesaurus 230 dans le systèm</t>
@@ -109,7 +109,7 @@
         <color indexed="11"/>
         <rFont val="Arial"/>
       </rPr>
-      <t>https://thesaurus.mom.fr/?idt=th230</t>
+      <t>https://thesaurus.mom.fr/?idt=th252</t>
     </r>
   </si>
   <si>
@@ -180,7 +180,7 @@
         <color indexed="11"/>
         <rFont val="Arial"/>
       </rPr>
-      <t>https://thesaurus.mom.fr/?idc=4283545&amp;idt=th230</t>
+      <t>https://thesaurus.mom.fr/?idc=4283545&amp;idt=th252</t>
     </r>
   </si>
   <si>
@@ -193,7 +193,7 @@
     <t>0610487</t>
   </si>
   <si>
-    <t>https://thesaurus.mom.fr/?idc=4283545&amp;idt=th230</t>
+    <t>https://thesaurus.mom.fr/?idc=4283545&amp;idt=th252</t>
   </si>
   <si>
     <t>069261</t>
@@ -248,7 +248,7 @@
         <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://thesaurus.mom.fr/?idc=4287899&amp;idt=th230</t>
+      <t>https://thesaurus.mom.fr/?idc=4287899&amp;idt=th252</t>
     </r>
   </si>
   <si>
@@ -289,7 +289,7 @@
         <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://thesaurus.mom.fr/?idc=4287975&amp;idt=th230</t>
+      <t>https://thesaurus.mom.fr/?idc=4287975&amp;idt=th252</t>
     </r>
   </si>
   <si>
@@ -366,7 +366,7 @@
         <color indexed="11"/>
         <rFont val="Arial"/>
       </rPr>
-      <t>https://thesaurus.mom.fr/?idc=4287979&amp;idt=th230</t>
+      <t>https://thesaurus.mom.fr/?idc=4287979&amp;idt=th252</t>
     </r>
   </si>
   <si>
@@ -428,7 +428,7 @@
         <color indexed="11"/>
         <rFont val="Arial"/>
       </rPr>
-      <t>https://thesaurus.mom.fr/?idc=4287976&amp;idt=th230</t>
+      <t>https://thesaurus.mom.fr/?idc=4287976&amp;idt=th252</t>
     </r>
   </si>
   <si>
@@ -475,7 +475,7 @@
         <color indexed="11"/>
         <rFont val="Arial"/>
       </rPr>
-      <t>https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230</t>
+      <t>https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252</t>
     </r>
   </si>
   <si>
@@ -486,7 +486,7 @@
         <color indexed="11"/>
         <rFont val="Arial"/>
       </rPr>
-      <t>https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230</t>
+      <t>https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252</t>
     </r>
   </si>
   <si>
@@ -529,7 +529,7 @@
         <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://thesaurus.mom.fr/?idc=4287744&amp;idt=th230</t>
+      <t>https://thesaurus.mom.fr/?idc=4287744&amp;idt=th252</t>
     </r>
   </si>
   <si>
@@ -546,7 +546,7 @@
         <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://thesaurus.mom.fr/?idc=4287682&amp;idt=th230</t>
+      <t>https://thesaurus.mom.fr/?idc=4287682&amp;idt=th252</t>
     </r>
   </si>
   <si>
@@ -627,7 +627,7 @@
         <color indexed="11"/>
         <rFont val="Arial"/>
       </rPr>
-      <t>https://thesaurus.mom.fr/?idc=4287639&amp;idt=th230</t>
+      <t>https://thesaurus.mom.fr/?idc=4287639&amp;idt=th252</t>
     </r>
   </si>
   <si>
@@ -655,7 +655,7 @@
         <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://thesaurus.mom.fr/?idc=4287680&amp;idt=th230</t>
+      <t>https://thesaurus.mom.fr/?idc=4287680&amp;idt=th252</t>
     </r>
   </si>
   <si>
@@ -686,7 +686,7 @@
     <t>1018</t>
   </si>
   <si>
-    <t>Remblais étalés pour partie, en poche concentrée pour une https://thesaurus.mom.fr/?idc=4287744&amp;idt=th230 partie sur le tuyau de fonte 1021, constitués de silex de calibre varié (maximum 30 cm de côté), pris dans une terre limoneuse plus ou moins pulvérulente avec des fragments de mortier et des boulettes d'argile orangée, des graviers de silex, des fragments de fonte; Démolition étalée, puis compactée de l'ancien château d'eau détruit il y a 35 ans environ;</t>
+    <t>Remblais étalés pour partie, en poche concentrée pour une https://thesaurus.mom.fr/?idc=4287744&amp;idt=th252 partie sur le tuyau de fonte 1021, constitués de silex de calibre varié (maximum 30 cm de côté), pris dans une terre limoneuse plus ou moins pulvérulente avec des fragments de mortier et des boulettes d'argile orangée, des graviers de silex, des fragments de fonte; Démolition étalée, puis compactée de l'ancien château d'eau détruit il y a 35 ans environ;</t>
   </si>
   <si>
     <r>
@@ -696,7 +696,7 @@
         <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://thesaurus.mom.fr/?idc=4287679&amp;idt=th230</t>
+      <t>https://thesaurus.mom.fr/?idc=4287679&amp;idt=th252</t>
     </r>
   </si>
   <si>
@@ -725,7 +725,7 @@
         <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://thesaurus.mom.fr/?idc=4287708&amp;idt=th230</t>
+      <t>https://thesaurus.mom.fr/?idc=4287708&amp;idt=th252</t>
     </r>
   </si>
   <si>
@@ -911,7 +911,7 @@
         <color indexed="11"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
-      <t>https://thesaurus.mom.fr/?idc=4287629&amp;idt=th230</t>
+      <t>https://thesaurus.mom.fr/?idc=4287629&amp;idt=th252</t>
     </r>
   </si>
   <si>
@@ -1058,11 +1058,11 @@
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
-      <t>https://thesaurus.mom.fr/?idc=4286251&amp;idt=th230</t>
+      <t>https://thesaurus.mom.fr/?idc=4286251&amp;idt=th252</t>
     </r>
   </si>
   <si>
-    <t>https://thesaurus.mom.fr/?idc=4287991&amp;idt=th230</t>
+    <t>https://thesaurus.mom.fr/?idc=4287991&amp;idt=th252</t>
   </si>
   <si>
     <r>
@@ -1072,7 +1072,7 @@
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
-      <t>https://thesaurus.mom.fr/?idc=4287997&amp;idt=th230</t>
+      <t>https://thesaurus.mom.fr/?idc=4287997&amp;idt=th252</t>
     </r>
   </si>
   <si>
@@ -1097,7 +1097,7 @@
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
-      <t>https://thesaurus.mom.fr/?idc=4287991&amp;idt=th230</t>
+      <t>https://thesaurus.mom.fr/?idc=4287991&amp;idt=th252</t>
     </r>
   </si>
   <si>
@@ -1108,7 +1108,7 @@
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
-      <t>https://thesaurus.mom.fr/?idc=4287998&amp;idt=th230</t>
+      <t>https://thesaurus.mom.fr/?idc=4287998&amp;idt=th252</t>
     </r>
   </si>
   <si>
@@ -1122,7 +1122,7 @@
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
-      <t>https://thesaurus.mom.fr/?idc=4286252&amp;idt=th230</t>
+      <t>https://thesaurus.mom.fr/?idc=4286252&amp;idt=th252</t>
     </r>
   </si>
   <si>
@@ -1133,7 +1133,7 @@
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
-      <t>https://thesaurus.mom.fr/?idc=4282395&amp;idt=th230</t>
+      <t>https://thesaurus.mom.fr/?idc=4282395&amp;idt=th252</t>
     </r>
   </si>
   <si>
@@ -1144,7 +1144,7 @@
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
-      <t>https://thesaurus.mom.fr/?idc=4287999&amp;idt=th230</t>
+      <t>https://thesaurus.mom.fr/?idc=4287999&amp;idt=th252</t>
     </r>
   </si>
   <si>
@@ -1172,7 +1172,7 @@
     <t>Incertain</t>
   </si>
   <si>
-    <t>https://thesaurus.mom.fr/?idc=4287648&amp;idt=th230</t>
+    <t>https://thesaurus.mom.fr/?idc=4287648&amp;idt=th252</t>
   </si>
   <si>
     <t>False</t>
@@ -1181,7 +1181,7 @@
     <t>True</t>
   </si>
   <si>
-    <t>https://thesaurus.mom.fr/?idc=4287647&amp;idt=th230</t>
+    <t>https://thesaurus.mom.fr/?idc=4287647&amp;idt=th252</t>
   </si>
   <si>
     <t>1047</t>
@@ -3495,7 +3495,7 @@
     <hyperlink ref="D2" r:id="rId1" location="" tooltip="" display="admin@siamois.fr"/>
     <hyperlink ref="E2" r:id="rId2" location="" tooltip="" display="https://thesaurus.mom.fr/?idt=th258"/>
     <hyperlink ref="E3" r:id="rId3" location="" tooltip="" display="https://thesaurus.mom.fr/?idt=th240"/>
-    <hyperlink ref="E4" r:id="rId4" location="" tooltip="" display="https://thesaurus.mom.fr/?idt=th230"/>
+    <hyperlink ref="E4" r:id="rId4" location="" tooltip="" display="https://thesaurus.mom.fr/?idt=th252"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
@@ -18204,9 +18204,9 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4283545&amp;idt=th230"/>
-    <hyperlink ref="B3" r:id="rId2" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4283545&amp;idt=th230"/>
-    <hyperlink ref="B4" r:id="rId3" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4283545&amp;idt=th230"/>
+    <hyperlink ref="B2" r:id="rId1" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4283545&amp;idt=th252"/>
+    <hyperlink ref="B3" r:id="rId2" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4283545&amp;idt=th252"/>
+    <hyperlink ref="B4" r:id="rId3" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4283545&amp;idt=th252"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
@@ -30483,20 +30483,20 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287899&amp;idt=th230"/>
-    <hyperlink ref="D3" r:id="rId2" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287899&amp;idt=th230"/>
-    <hyperlink ref="D4" r:id="rId3" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287899&amp;idt=th230"/>
-    <hyperlink ref="D5" r:id="rId4" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287899&amp;idt=th230"/>
-    <hyperlink ref="D6" r:id="rId5" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287975&amp;idt=th230"/>
-    <hyperlink ref="D7" r:id="rId6" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287975&amp;idt=th230"/>
-    <hyperlink ref="D8" r:id="rId7" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287899&amp;idt=th230"/>
-    <hyperlink ref="D9" r:id="rId8" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287899&amp;idt=th230"/>
-    <hyperlink ref="D10" r:id="rId9" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287975&amp;idt=th230"/>
-    <hyperlink ref="D11" r:id="rId10" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287975&amp;idt=th230"/>
-    <hyperlink ref="D12" r:id="rId11" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287975&amp;idt=th230"/>
-    <hyperlink ref="D13" r:id="rId12" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287899&amp;idt=th230"/>
-    <hyperlink ref="D14" r:id="rId13" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287975&amp;idt=th230"/>
-    <hyperlink ref="D15" r:id="rId14" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287975&amp;idt=th230"/>
+    <hyperlink ref="D2" r:id="rId1" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287899&amp;idt=th252"/>
+    <hyperlink ref="D3" r:id="rId2" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287899&amp;idt=th252"/>
+    <hyperlink ref="D4" r:id="rId3" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287899&amp;idt=th252"/>
+    <hyperlink ref="D5" r:id="rId4" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287899&amp;idt=th252"/>
+    <hyperlink ref="D6" r:id="rId5" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287975&amp;idt=th252"/>
+    <hyperlink ref="D7" r:id="rId6" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287975&amp;idt=th252"/>
+    <hyperlink ref="D8" r:id="rId7" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287899&amp;idt=th252"/>
+    <hyperlink ref="D9" r:id="rId8" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287899&amp;idt=th252"/>
+    <hyperlink ref="D10" r:id="rId9" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287975&amp;idt=th252"/>
+    <hyperlink ref="D11" r:id="rId10" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287975&amp;idt=th252"/>
+    <hyperlink ref="D12" r:id="rId11" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287975&amp;idt=th252"/>
+    <hyperlink ref="D13" r:id="rId12" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287899&amp;idt=th252"/>
+    <hyperlink ref="D14" r:id="rId13" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287975&amp;idt=th252"/>
+    <hyperlink ref="D15" r:id="rId14" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287975&amp;idt=th252"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
@@ -30828,25 +30828,25 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th230"/>
-    <hyperlink ref="B3" r:id="rId2" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th230"/>
-    <hyperlink ref="B4" r:id="rId3" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th230"/>
-    <hyperlink ref="B5" r:id="rId4" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th230"/>
-    <hyperlink ref="B6" r:id="rId5" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th230"/>
-    <hyperlink ref="B7" r:id="rId6" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th230"/>
-    <hyperlink ref="B8" r:id="rId7" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th230"/>
-    <hyperlink ref="B9" r:id="rId8" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th230"/>
-    <hyperlink ref="B10" r:id="rId9" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th230"/>
-    <hyperlink ref="B11" r:id="rId10" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th230"/>
-    <hyperlink ref="B12" r:id="rId11" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th230"/>
-    <hyperlink ref="B13" r:id="rId12" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th230"/>
-    <hyperlink ref="B14" r:id="rId13" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th230"/>
-    <hyperlink ref="B15" r:id="rId14" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th230"/>
-    <hyperlink ref="B16" r:id="rId15" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th230"/>
-    <hyperlink ref="B17" r:id="rId16" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th230"/>
-    <hyperlink ref="B18" r:id="rId17" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th230"/>
-    <hyperlink ref="B19" r:id="rId18" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th230"/>
-    <hyperlink ref="B20" r:id="rId19" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287976&amp;idt=th230"/>
+    <hyperlink ref="B2" r:id="rId1" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th252"/>
+    <hyperlink ref="B3" r:id="rId2" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th252"/>
+    <hyperlink ref="B4" r:id="rId3" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th252"/>
+    <hyperlink ref="B5" r:id="rId4" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th252"/>
+    <hyperlink ref="B6" r:id="rId5" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th252"/>
+    <hyperlink ref="B7" r:id="rId6" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th252"/>
+    <hyperlink ref="B8" r:id="rId7" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th252"/>
+    <hyperlink ref="B9" r:id="rId8" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th252"/>
+    <hyperlink ref="B10" r:id="rId9" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th252"/>
+    <hyperlink ref="B11" r:id="rId10" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th252"/>
+    <hyperlink ref="B12" r:id="rId11" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th252"/>
+    <hyperlink ref="B13" r:id="rId12" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th252"/>
+    <hyperlink ref="B14" r:id="rId13" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th252"/>
+    <hyperlink ref="B15" r:id="rId14" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th252"/>
+    <hyperlink ref="B16" r:id="rId15" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th252"/>
+    <hyperlink ref="B17" r:id="rId16" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th252"/>
+    <hyperlink ref="B18" r:id="rId17" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th252"/>
+    <hyperlink ref="B19" r:id="rId18" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287979&amp;idt=th252"/>
+    <hyperlink ref="B20" r:id="rId19" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287976&amp;idt=th252"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
@@ -47201,159 +47201,159 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D2" r:id="rId2" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
+    <hyperlink ref="C2" r:id="rId1" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D2" r:id="rId2" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
     <hyperlink ref="F2" r:id="rId3" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287983&amp;idt=th240"/>
-    <hyperlink ref="C3" r:id="rId4" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D3" r:id="rId5" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
+    <hyperlink ref="C3" r:id="rId4" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D3" r:id="rId5" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
     <hyperlink ref="F3" r:id="rId6" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287983&amp;idt=th240"/>
-    <hyperlink ref="C4" r:id="rId7" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D4" r:id="rId8" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
+    <hyperlink ref="C4" r:id="rId7" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D4" r:id="rId8" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
     <hyperlink ref="F4" r:id="rId9" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287983&amp;idt=th240"/>
-    <hyperlink ref="C5" r:id="rId10" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D5" r:id="rId11" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
-    <hyperlink ref="F5" r:id="rId12" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287744&amp;idt=th230"/>
-    <hyperlink ref="C6" r:id="rId13" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D6" r:id="rId14" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
-    <hyperlink ref="F6" r:id="rId15" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287682&amp;idt=th230"/>
-    <hyperlink ref="C7" r:id="rId16" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D7" r:id="rId17" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
+    <hyperlink ref="C5" r:id="rId10" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D5" r:id="rId11" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
+    <hyperlink ref="F5" r:id="rId12" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287744&amp;idt=th252"/>
+    <hyperlink ref="C6" r:id="rId13" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D6" r:id="rId14" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
+    <hyperlink ref="F6" r:id="rId15" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287682&amp;idt=th252"/>
+    <hyperlink ref="C7" r:id="rId16" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D7" r:id="rId17" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
     <hyperlink ref="F7" r:id="rId18" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287984&amp;idt=th240"/>
-    <hyperlink ref="C8" r:id="rId19" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D8" r:id="rId20" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
+    <hyperlink ref="C8" r:id="rId19" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D8" r:id="rId20" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
     <hyperlink ref="F8" r:id="rId21" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287984&amp;idt=th240"/>
-    <hyperlink ref="C9" r:id="rId22" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D9" r:id="rId23" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
-    <hyperlink ref="F9" r:id="rId24" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287682&amp;idt=th230"/>
-    <hyperlink ref="C10" r:id="rId25" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D10" r:id="rId26" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
+    <hyperlink ref="C9" r:id="rId22" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D9" r:id="rId23" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
+    <hyperlink ref="F9" r:id="rId24" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287682&amp;idt=th252"/>
+    <hyperlink ref="C10" r:id="rId25" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D10" r:id="rId26" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
     <hyperlink ref="F10" r:id="rId27" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287985&amp;idt=th240"/>
-    <hyperlink ref="C11" r:id="rId28" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D11" r:id="rId29" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
-    <hyperlink ref="F11" r:id="rId30" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287682&amp;idt=th230"/>
-    <hyperlink ref="C12" r:id="rId31" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D12" r:id="rId32" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
+    <hyperlink ref="C11" r:id="rId28" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D11" r:id="rId29" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
+    <hyperlink ref="F11" r:id="rId30" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287682&amp;idt=th252"/>
+    <hyperlink ref="C12" r:id="rId31" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D12" r:id="rId32" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
     <hyperlink ref="F12" r:id="rId33" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287983&amp;idt=th240"/>
-    <hyperlink ref="C13" r:id="rId34" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D13" r:id="rId35" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
-    <hyperlink ref="F13" r:id="rId36" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287682&amp;idt=th230"/>
-    <hyperlink ref="C14" r:id="rId37" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D14" r:id="rId38" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287639&amp;idt=th230"/>
+    <hyperlink ref="C13" r:id="rId34" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D13" r:id="rId35" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
+    <hyperlink ref="F13" r:id="rId36" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287682&amp;idt=th252"/>
+    <hyperlink ref="C14" r:id="rId37" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D14" r:id="rId38" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287639&amp;idt=th252"/>
     <hyperlink ref="F14" r:id="rId39" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287540&amp;idt=th240"/>
-    <hyperlink ref="C15" r:id="rId40" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D15" r:id="rId41" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
-    <hyperlink ref="F15" r:id="rId42" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287680&amp;idt=th230"/>
-    <hyperlink ref="C16" r:id="rId43" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D16" r:id="rId44" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287639&amp;idt=th230"/>
+    <hyperlink ref="C15" r:id="rId40" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D15" r:id="rId41" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
+    <hyperlink ref="F15" r:id="rId42" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287680&amp;idt=th252"/>
+    <hyperlink ref="C16" r:id="rId43" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D16" r:id="rId44" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287639&amp;idt=th252"/>
     <hyperlink ref="F16" r:id="rId45" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287540&amp;idt=th240"/>
-    <hyperlink ref="C17" r:id="rId46" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D17" r:id="rId47" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287639&amp;idt=th230"/>
+    <hyperlink ref="C17" r:id="rId46" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D17" r:id="rId47" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287639&amp;idt=th252"/>
     <hyperlink ref="F17" r:id="rId48" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287540&amp;idt=th240"/>
-    <hyperlink ref="C18" r:id="rId49" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D18" r:id="rId50" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
-    <hyperlink ref="F18" r:id="rId51" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287744&amp;idt=th230"/>
-    <hyperlink ref="C19" r:id="rId52" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D19" r:id="rId53" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
-    <hyperlink ref="F19" r:id="rId54" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287744&amp;idt=th230"/>
-    <hyperlink ref="C20" r:id="rId55" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D20" r:id="rId56" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
-    <hyperlink ref="F20" r:id="rId57" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287679&amp;idt=th230"/>
-    <hyperlink ref="C21" r:id="rId58" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D21" r:id="rId59" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
-    <hyperlink ref="F21" r:id="rId60" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287680&amp;idt=th230"/>
-    <hyperlink ref="C22" r:id="rId61" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D22" r:id="rId62" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
+    <hyperlink ref="C18" r:id="rId49" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D18" r:id="rId50" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
+    <hyperlink ref="F18" r:id="rId51" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287744&amp;idt=th252"/>
+    <hyperlink ref="C19" r:id="rId52" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D19" r:id="rId53" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
+    <hyperlink ref="F19" r:id="rId54" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287744&amp;idt=th252"/>
+    <hyperlink ref="C20" r:id="rId55" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D20" r:id="rId56" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
+    <hyperlink ref="F20" r:id="rId57" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287679&amp;idt=th252"/>
+    <hyperlink ref="C21" r:id="rId58" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D21" r:id="rId59" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
+    <hyperlink ref="F21" r:id="rId60" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287680&amp;idt=th252"/>
+    <hyperlink ref="C22" r:id="rId61" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D22" r:id="rId62" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
     <hyperlink ref="F22" r:id="rId63" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287984&amp;idt=th240"/>
-    <hyperlink ref="C23" r:id="rId64" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D23" r:id="rId65" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
-    <hyperlink ref="F23" r:id="rId66" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287708&amp;idt=th230"/>
-    <hyperlink ref="C24" r:id="rId67" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D24" r:id="rId68" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287639&amp;idt=th230"/>
+    <hyperlink ref="C23" r:id="rId64" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D23" r:id="rId65" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
+    <hyperlink ref="F23" r:id="rId66" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287708&amp;idt=th252"/>
+    <hyperlink ref="C24" r:id="rId67" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D24" r:id="rId68" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287639&amp;idt=th252"/>
     <hyperlink ref="F24" r:id="rId69" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287540&amp;idt=th240"/>
-    <hyperlink ref="C25" r:id="rId70" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D25" r:id="rId71" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
+    <hyperlink ref="C25" r:id="rId70" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D25" r:id="rId71" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
     <hyperlink ref="F25" r:id="rId72" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287754&amp;idt=th240"/>
-    <hyperlink ref="C26" r:id="rId73" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D26" r:id="rId74" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
+    <hyperlink ref="C26" r:id="rId73" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D26" r:id="rId74" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
     <hyperlink ref="F26" r:id="rId75" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287985&amp;idt=th240"/>
-    <hyperlink ref="C27" r:id="rId76" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D27" r:id="rId77" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
-    <hyperlink ref="F27" r:id="rId78" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287708&amp;idt=th230"/>
-    <hyperlink ref="C28" r:id="rId79" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D28" r:id="rId80" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
-    <hyperlink ref="F28" r:id="rId81" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287744&amp;idt=th230"/>
-    <hyperlink ref="C29" r:id="rId82" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D29" r:id="rId83" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287639&amp;idt=th230"/>
+    <hyperlink ref="C27" r:id="rId76" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D27" r:id="rId77" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
+    <hyperlink ref="F27" r:id="rId78" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287708&amp;idt=th252"/>
+    <hyperlink ref="C28" r:id="rId79" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D28" r:id="rId80" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
+    <hyperlink ref="F28" r:id="rId81" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287744&amp;idt=th252"/>
+    <hyperlink ref="C29" r:id="rId82" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D29" r:id="rId83" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287639&amp;idt=th252"/>
     <hyperlink ref="F29" r:id="rId84" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287540&amp;idt=th240"/>
-    <hyperlink ref="C30" r:id="rId85" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D30" r:id="rId86" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
-    <hyperlink ref="F30" r:id="rId87" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287708&amp;idt=th230"/>
-    <hyperlink ref="C31" r:id="rId88" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D31" r:id="rId89" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
-    <hyperlink ref="F31" r:id="rId90" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287708&amp;idt=th230"/>
-    <hyperlink ref="C32" r:id="rId91" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D32" r:id="rId92" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
-    <hyperlink ref="F32" r:id="rId93" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287708&amp;idt=th230"/>
-    <hyperlink ref="C33" r:id="rId94" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D33" r:id="rId95" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
+    <hyperlink ref="C30" r:id="rId85" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D30" r:id="rId86" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
+    <hyperlink ref="F30" r:id="rId87" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287708&amp;idt=th252"/>
+    <hyperlink ref="C31" r:id="rId88" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D31" r:id="rId89" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
+    <hyperlink ref="F31" r:id="rId90" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287708&amp;idt=th252"/>
+    <hyperlink ref="C32" r:id="rId91" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D32" r:id="rId92" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
+    <hyperlink ref="F32" r:id="rId93" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287708&amp;idt=th252"/>
+    <hyperlink ref="C33" r:id="rId94" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D33" r:id="rId95" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
     <hyperlink ref="F33" r:id="rId96" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287754&amp;idt=th240"/>
-    <hyperlink ref="C34" r:id="rId97" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D34" r:id="rId98" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
+    <hyperlink ref="C34" r:id="rId97" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D34" r:id="rId98" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
     <hyperlink ref="F34" r:id="rId99" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287988&amp;idt=th240"/>
-    <hyperlink ref="C35" r:id="rId100" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D35" r:id="rId101" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
-    <hyperlink ref="F35" r:id="rId102" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287708&amp;idt=th230"/>
-    <hyperlink ref="C36" r:id="rId103" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D36" r:id="rId104" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
+    <hyperlink ref="C35" r:id="rId100" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D35" r:id="rId101" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
+    <hyperlink ref="F35" r:id="rId102" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287708&amp;idt=th252"/>
+    <hyperlink ref="C36" r:id="rId103" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D36" r:id="rId104" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
     <hyperlink ref="F36" r:id="rId105" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287988&amp;idt=th240"/>
-    <hyperlink ref="C37" r:id="rId106" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D37" r:id="rId107" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
-    <hyperlink ref="F37" r:id="rId108" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287708&amp;idt=th230"/>
-    <hyperlink ref="C38" r:id="rId109" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D38" r:id="rId110" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
-    <hyperlink ref="F38" r:id="rId111" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287708&amp;idt=th230"/>
-    <hyperlink ref="C39" r:id="rId112" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D39" r:id="rId113" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
+    <hyperlink ref="C37" r:id="rId106" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D37" r:id="rId107" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
+    <hyperlink ref="F37" r:id="rId108" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287708&amp;idt=th252"/>
+    <hyperlink ref="C38" r:id="rId109" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D38" r:id="rId110" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
+    <hyperlink ref="F38" r:id="rId111" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287708&amp;idt=th252"/>
+    <hyperlink ref="C39" r:id="rId112" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D39" r:id="rId113" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
     <hyperlink ref="F39" r:id="rId114" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287754&amp;idt=th240"/>
-    <hyperlink ref="C40" r:id="rId115" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D40" r:id="rId116" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
-    <hyperlink ref="F40" r:id="rId117" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287708&amp;idt=th230"/>
-    <hyperlink ref="C41" r:id="rId118" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D41" r:id="rId119" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
-    <hyperlink ref="F41" r:id="rId120" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287680&amp;idt=th230"/>
-    <hyperlink ref="C42" r:id="rId121" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D42" r:id="rId122" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
-    <hyperlink ref="F42" r:id="rId123" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287708&amp;idt=th230"/>
-    <hyperlink ref="C43" r:id="rId124" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D43" r:id="rId125" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
-    <hyperlink ref="F43" r:id="rId126" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287682&amp;idt=th230"/>
-    <hyperlink ref="C44" r:id="rId127" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D44" r:id="rId128" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
+    <hyperlink ref="C40" r:id="rId115" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D40" r:id="rId116" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
+    <hyperlink ref="F40" r:id="rId117" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287708&amp;idt=th252"/>
+    <hyperlink ref="C41" r:id="rId118" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D41" r:id="rId119" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
+    <hyperlink ref="F41" r:id="rId120" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287680&amp;idt=th252"/>
+    <hyperlink ref="C42" r:id="rId121" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D42" r:id="rId122" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
+    <hyperlink ref="F42" r:id="rId123" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287708&amp;idt=th252"/>
+    <hyperlink ref="C43" r:id="rId124" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D43" r:id="rId125" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
+    <hyperlink ref="F43" r:id="rId126" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287682&amp;idt=th252"/>
+    <hyperlink ref="C44" r:id="rId127" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D44" r:id="rId128" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
     <hyperlink ref="F44" r:id="rId129" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287984&amp;idt=th240"/>
-    <hyperlink ref="C45" r:id="rId130" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D45" r:id="rId131" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
-    <hyperlink ref="F45" r:id="rId132" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287708&amp;idt=th230"/>
-    <hyperlink ref="C46" r:id="rId133" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D46" r:id="rId134" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
-    <hyperlink ref="F46" r:id="rId135" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287708&amp;idt=th230"/>
-    <hyperlink ref="C47" r:id="rId136" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D47" r:id="rId137" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287639&amp;idt=th230"/>
+    <hyperlink ref="C45" r:id="rId130" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D45" r:id="rId131" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
+    <hyperlink ref="F45" r:id="rId132" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287708&amp;idt=th252"/>
+    <hyperlink ref="C46" r:id="rId133" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D46" r:id="rId134" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
+    <hyperlink ref="F46" r:id="rId135" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287708&amp;idt=th252"/>
+    <hyperlink ref="C47" r:id="rId136" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D47" r:id="rId137" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287639&amp;idt=th252"/>
     <hyperlink ref="F47" r:id="rId138" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287540&amp;idt=th240"/>
-    <hyperlink ref="C48" r:id="rId139" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th230"/>
-    <hyperlink ref="D48" r:id="rId140" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th230"/>
-    <hyperlink ref="F48" r:id="rId141" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287680&amp;idt=th230"/>
-    <hyperlink ref="C49" r:id="rId142" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th230"/>
-    <hyperlink ref="C50" r:id="rId143" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th230"/>
-    <hyperlink ref="C51" r:id="rId144" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th230"/>
-    <hyperlink ref="C52" r:id="rId145" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th230"/>
-    <hyperlink ref="C53" r:id="rId146" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th230"/>
-    <hyperlink ref="C54" r:id="rId147" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th230"/>
-    <hyperlink ref="C55" r:id="rId148" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th230"/>
-    <hyperlink ref="C56" r:id="rId149" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th230"/>
-    <hyperlink ref="C57" r:id="rId150" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th230"/>
-    <hyperlink ref="C58" r:id="rId151" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th230"/>
-    <hyperlink ref="C59" r:id="rId152" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th230"/>
-    <hyperlink ref="C60" r:id="rId153" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th230"/>
+    <hyperlink ref="C48" r:id="rId139" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287627&amp;idt=th252"/>
+    <hyperlink ref="D48" r:id="rId140" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287638&amp;idt=th252"/>
+    <hyperlink ref="F48" r:id="rId141" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287680&amp;idt=th252"/>
+    <hyperlink ref="C49" r:id="rId142" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th252"/>
+    <hyperlink ref="C50" r:id="rId143" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th252"/>
+    <hyperlink ref="C51" r:id="rId144" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th252"/>
+    <hyperlink ref="C52" r:id="rId145" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th252"/>
+    <hyperlink ref="C53" r:id="rId146" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th252"/>
+    <hyperlink ref="C54" r:id="rId147" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th252"/>
+    <hyperlink ref="C55" r:id="rId148" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th252"/>
+    <hyperlink ref="C56" r:id="rId149" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th252"/>
+    <hyperlink ref="C57" r:id="rId150" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th252"/>
+    <hyperlink ref="C58" r:id="rId151" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th252"/>
+    <hyperlink ref="C59" r:id="rId152" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th252"/>
+    <hyperlink ref="C60" r:id="rId153" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287629&amp;idt=th252"/>
     <hyperlink ref="C61" r:id="rId154" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4289298&amp;idt=th258"/>
     <hyperlink ref="C62" r:id="rId155" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4289298&amp;idt=th258"/>
     <hyperlink ref="C63" r:id="rId156" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4289298&amp;idt=th258"/>
@@ -56928,18 +56928,18 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4286251&amp;idt=th230"/>
-    <hyperlink ref="D2" r:id="rId2" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287997&amp;idt=th230"/>
+    <hyperlink ref="B2" r:id="rId1" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4286251&amp;idt=th252"/>
+    <hyperlink ref="D2" r:id="rId2" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287997&amp;idt=th252"/>
     <hyperlink ref="F2" r:id="rId3" location="" tooltip="" display="pascal.gibut@siamois.fr"/>
     <hyperlink ref="G2" r:id="rId4" location="" tooltip="" display="pascal.gibut@siamois.fr"/>
-    <hyperlink ref="B3" r:id="rId5" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4286251&amp;idt=th230"/>
-    <hyperlink ref="C3" r:id="rId6" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287991&amp;idt=th230"/>
-    <hyperlink ref="D3" r:id="rId7" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287998&amp;idt=th230"/>
+    <hyperlink ref="B3" r:id="rId5" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4286251&amp;idt=th252"/>
+    <hyperlink ref="C3" r:id="rId6" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287991&amp;idt=th252"/>
+    <hyperlink ref="D3" r:id="rId7" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287998&amp;idt=th252"/>
     <hyperlink ref="F3" r:id="rId8" location="" tooltip="" display="pascal.gibut@siamois.fr"/>
     <hyperlink ref="G3" r:id="rId9" location="" tooltip="" display="pascal.gibut@siamois.fr"/>
-    <hyperlink ref="B4" r:id="rId10" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4286252&amp;idt=th230"/>
-    <hyperlink ref="C4" r:id="rId11" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4282395&amp;idt=th230"/>
-    <hyperlink ref="D4" r:id="rId12" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287999&amp;idt=th230"/>
+    <hyperlink ref="B4" r:id="rId10" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4286252&amp;idt=th252"/>
+    <hyperlink ref="C4" r:id="rId11" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4282395&amp;idt=th252"/>
+    <hyperlink ref="D4" r:id="rId12" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287999&amp;idt=th252"/>
     <hyperlink ref="F4" r:id="rId13" location="" tooltip="" display="pascal.gibut@siamois.fr"/>
     <hyperlink ref="G4" r:id="rId14" location="" tooltip="" display="pascal.gibut@siamois.fr"/>
   </hyperlinks>
